--- a/NOBA bank modell.xlsx
+++ b/NOBA bank modell.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE26AF03-3359-534D-99DB-10B0B576D167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BDA6ED5-CD08-FC46-9C85-180EC21F23B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="26120" windowHeight="26740" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
+    <workbookView xWindow="25080" yWindow="500" windowWidth="26120" windowHeight="26740" activeTab="4" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
     <sheet name="Modell" sheetId="2" r:id="rId2"/>
     <sheet name="Segementer" sheetId="4" r:id="rId3"/>
-    <sheet name="Kapitalbro" sheetId="11" r:id="rId4"/>
-    <sheet name="Kvalitet bok (Gross)" sheetId="7" r:id="rId5"/>
-    <sheet name="Kvalitet bok (provisons)" sheetId="9" r:id="rId6"/>
-    <sheet name="Net credit losses" sheetId="8" r:id="rId7"/>
-    <sheet name="Funding" sheetId="10" r:id="rId8"/>
-    <sheet name="Nøkkeltall" sheetId="3" r:id="rId9"/>
-    <sheet name="Nedsideberegning" sheetId="5" r:id="rId10"/>
+    <sheet name="Segmenter P L" sheetId="12" r:id="rId4"/>
+    <sheet name="Kapitalbro" sheetId="11" r:id="rId5"/>
+    <sheet name="Kvalitet bok (Gross)" sheetId="7" r:id="rId6"/>
+    <sheet name="Kvalitet bok (provisons)" sheetId="9" r:id="rId7"/>
+    <sheet name="Net credit losses" sheetId="8" r:id="rId8"/>
+    <sheet name="Funding" sheetId="10" r:id="rId9"/>
+    <sheet name="Nøkkeltall" sheetId="3" r:id="rId10"/>
+    <sheet name="Nedsideberegning" sheetId="5" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -148,12 +149,21 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={60E1B239-6144-9348-AE77-E724BB0F9BB1}</author>
     <author>tc={2DC4CC7C-6D86-6F4A-8262-8E4D3EE125FA}</author>
     <author>tc={9DA7037A-30F2-214C-A929-C6C3B95CF35D}</author>
     <author>tc={AE62A832-84BC-4248-B5DF-EDBF609448B7}</author>
   </authors>
   <commentList>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{2DC4CC7C-6D86-6F4A-8262-8E4D3EE125FA}">
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{60E1B239-6144-9348-AE77-E724BB0F9BB1}">
+      <text>
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
+    NOBA ønsker å ligge i lave enden av rangen 13-15%</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="1" shapeId="0" xr:uid="{2DC4CC7C-6D86-6F4A-8262-8E4D3EE125FA}">
       <text>
         <t>[Kommentartråd]
 Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
@@ -161,7 +171,7 @@
     Forutsetter lik som Q226</t>
       </text>
     </comment>
-    <comment ref="B16" authorId="1" shapeId="0" xr:uid="{9DA7037A-30F2-214C-A929-C6C3B95CF35D}">
+    <comment ref="B16" authorId="2" shapeId="0" xr:uid="{9DA7037A-30F2-214C-A929-C6C3B95CF35D}">
       <text>
         <t>[Kommentartråd]
 Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
@@ -169,7 +179,7 @@
     Hvor mye kapital NOBA må ha bak veksten sin</t>
       </text>
     </comment>
-    <comment ref="B17" authorId="2" shapeId="0" xr:uid="{AE62A832-84BC-4248-B5DF-EDBF609448B7}">
+    <comment ref="B17" authorId="3" shapeId="0" xr:uid="{AE62A832-84BC-4248-B5DF-EDBF609448B7}">
       <text>
         <t>[Kommentartråd]
 Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
@@ -218,7 +228,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="245">
   <si>
     <t>Kapitalstruktur</t>
   </si>
@@ -535,9 +545,6 @@
     <t xml:space="preserve">Sales of shares </t>
   </si>
   <si>
-    <t>Acquisition in PP&amp;E and intangible ass</t>
-  </si>
-  <si>
     <t>CFFI</t>
   </si>
   <si>
@@ -866,6 +873,96 @@
   </si>
   <si>
     <t>Andelen av beløpet som er avsatt til tap</t>
+  </si>
+  <si>
+    <t>Nordax tilbyr:</t>
+  </si>
+  <si>
+    <t>Boliglån (Secured)</t>
+  </si>
+  <si>
+    <t>Bank Norwegian tilbyr:</t>
+  </si>
+  <si>
+    <t>kredittkort</t>
+  </si>
+  <si>
+    <t>Forbrukslån (Private loan)</t>
+  </si>
+  <si>
+    <t>Grønt lån (Private loan)</t>
+  </si>
+  <si>
+    <t>Rammelån (Secured/Priavte loan)</t>
+  </si>
+  <si>
+    <t>Svensk hypotekspension tilbyr:</t>
+  </si>
+  <si>
+    <t>Pantesikret equity release eller reverese mortgage</t>
+  </si>
+  <si>
+    <t>Øker belåningen på boligen din og får ut EK</t>
+  </si>
+  <si>
+    <t>Ingen amort eller renter, betales tilbake når huset selges eller ved dødsfall</t>
+  </si>
+  <si>
+    <t>Lånet akkumuleres helt til boligen selges eller døsfall og lånet kan ikke voerstige husets verdi. Stiger lånet over husets verdi er det NOBA tap</t>
+  </si>
+  <si>
+    <t>DBT tilbyr:</t>
+  </si>
+  <si>
+    <t>Bedriftslån fr 5-50 SEKm, 4,5% + STIBOR (Private loan)</t>
+  </si>
+  <si>
+    <t>Interest expenses</t>
+  </si>
+  <si>
+    <t>Commision expenses</t>
+  </si>
+  <si>
+    <t>net profit from finaancial trans</t>
+  </si>
+  <si>
+    <t>General admin expenses</t>
+  </si>
+  <si>
+    <t>operating profit</t>
+  </si>
+  <si>
+    <t>Profit attributable to Tier 1 cap</t>
+  </si>
+  <si>
+    <t>Shares</t>
+  </si>
+  <si>
+    <t>NIM</t>
+  </si>
+  <si>
+    <t>C/I</t>
+  </si>
+  <si>
+    <t>Cost of risk</t>
+  </si>
+  <si>
+    <t>Potensial yield%</t>
+  </si>
+  <si>
+    <t>Nordic capital er i styret, Christopher Ekdahl</t>
+  </si>
+  <si>
+    <t>Sampo er i styret, Richard Wennerklint</t>
+  </si>
+  <si>
+    <t>22.09.26: Sampo hat gjort et nedsalg på 14,7 mill aksjer til ish 85,2 SEK, eier nå 10,01%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.02.26: Nordic cap og Sampo selger 50 mill aksjer total til 100SEK/aksje. Nordic cap 40 og Sampo 10. </t>
+  </si>
+  <si>
+    <t>Capex</t>
   </si>
 </sst>
 </file>
@@ -882,7 +979,7 @@
     <numFmt numFmtId="170" formatCode="[$SEK]\ #,##0.00_);[Red]\([$SEK]\ #,##0.00\)"/>
     <numFmt numFmtId="171" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -988,6 +1085,14 @@
     <font>
       <sz val="14"/>
       <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1105,7 +1210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1169,7 +1274,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
@@ -1226,6 +1330,25 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1607,7 +1730,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="August Hodt" id="{ED9CD82B-6389-4241-9649-653FEDD52C0B}" userId="a530012ce760c12d" providerId="Windows Live"/>
+  <person displayName="august hodt" id="{ED9CD82B-6389-4241-9649-653FEDD52C0B}" userId="a530012ce760c12d" providerId="Windows Live"/>
   <person displayName="(Student) Hodt, August" id="{87E5C055-FB23-5444-8A46-0D252F67019F}" userId="S::s2511823@bi.no::44d2ca7c-c877-4b52-8217-c5df9fee6d96" providerId="AD"/>
 </personList>
 </file>
@@ -1948,6 +2071,9 @@
 
 <file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B6" dT="2026-09-17T13:25:48.56" personId="{ED9CD82B-6389-4241-9649-653FEDD52C0B}" id="{60E1B239-6144-9348-AE77-E724BB0F9BB1}">
+    <text>NOBA ønsker å ligge i lave enden av rangen 13-15%</text>
+  </threadedComment>
   <threadedComment ref="B8" dT="2026-09-13T19:05:51.34" personId="{ED9CD82B-6389-4241-9649-653FEDD52C0B}" id="{2DC4CC7C-6D86-6F4A-8262-8E4D3EE125FA}">
     <text>Forutsetter lik som Q226</text>
   </threadedComment>
@@ -2000,7 +2126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6FABC2-1253-924E-8CB2-F0C03750A097}">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:X47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="10.83203125" style="2"/>
@@ -2008,84 +2134,171 @@
     <col min="8" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="I1" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X3" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X4" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="X5" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="X7" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="X8" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X9" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X10" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X11" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X13" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X14" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X15" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X16" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X17" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="X19" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X20" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="I26" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M27" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M28" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>208</v>
+        <v>242</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -2095,6 +2308,50 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEC8E745-DC06-8448-81B5-DC40131426CF}">
+  <dimension ref="C4:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:6" ht="62" x14ac:dyDescent="0.7">
+      <c r="C4" s="7"/>
+      <c r="D4" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E4" s="7">
+        <v>2027</v>
+      </c>
+      <c r="F4" s="7">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="5" spans="3:6" ht="62" x14ac:dyDescent="0.7">
+      <c r="C5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="33">
+        <f>Modell!$B$4/Modell!AD22</f>
+        <v>10.295002087730653</v>
+      </c>
+      <c r="E5" s="33">
+        <f>Modell!$B$4/Modell!AE22</f>
+        <v>8.4794854821743009</v>
+      </c>
+      <c r="F5" s="33">
+        <f>Modell!$B$4/Modell!AF22</f>
+        <v>7.4713293470119249</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3E88D3-8920-4B4C-A6FE-8E4196A56417}">
   <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -2116,100 +2373,100 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C11" s="74"/>
+      <c r="C11" s="73"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C12" s="74"/>
+      <c r="C12" s="73"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C13" s="72"/>
+      <c r="C13" s="71"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C14" s="74"/>
+      <c r="C14" s="73"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C15" s="74"/>
+      <c r="C15" s="73"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C16" s="74"/>
+      <c r="C16" s="73"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C17" s="75"/>
+      <c r="C17" s="74"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C20" s="76"/>
-      <c r="D20" s="76"/>
-      <c r="E20" s="76"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="75"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C21" s="76"/>
-      <c r="D21" s="76"/>
-      <c r="E21" s="76"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C22" s="76"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="75"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C23" s="76"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C24" s="76"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C25" s="76"/>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
-      <c r="C26" s="77"/>
-      <c r="D26" s="77"/>
-      <c r="E26" s="77"/>
+      <c r="C26" s="76"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C29" s="76"/>
-      <c r="D29" s="76"/>
-      <c r="E29" s="76"/>
+      <c r="C29" s="75"/>
+      <c r="D29" s="75"/>
+      <c r="E29" s="75"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C30" s="27"/>
@@ -2232,24 +2489,24 @@
       <c r="B34" s="1"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C35" s="76"/>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C36" s="76"/>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
+      <c r="C36" s="75"/>
+      <c r="D36" s="75"/>
+      <c r="E36" s="75"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C37" s="76"/>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
+      <c r="C37" s="75"/>
+      <c r="D37" s="75"/>
+      <c r="E37" s="75"/>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C38" s="76"/>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
+      <c r="C38" s="75"/>
+      <c r="D38" s="75"/>
+      <c r="E38" s="75"/>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="1"/>
@@ -2372,16 +2629,16 @@
         <v>30</v>
       </c>
       <c r="T3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="U3" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="V3" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="W3" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>120</v>
       </c>
       <c r="Y3" s="4" t="s">
         <v>72</v>
@@ -2398,7 +2655,7 @@
       <c r="AC3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="AD3" s="80" t="s">
+      <c r="AD3" s="79" t="s">
         <v>17</v>
       </c>
       <c r="AE3" s="4" t="s">
@@ -2434,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>40</v>
@@ -2483,6 +2740,7 @@
       <c r="U4" s="15">
         <v>3864</v>
       </c>
+      <c r="V4" s="15"/>
       <c r="W4" s="15"/>
       <c r="X4" s="15"/>
       <c r="Y4" s="15">
@@ -2549,7 +2807,7 @@
         <v>500</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
@@ -2659,7 +2917,7 @@
       </c>
       <c r="B6" s="8">
         <f>B4*B5</f>
-        <v>43500</v>
+        <v>43000</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>41</v>
@@ -2758,7 +3016,7 @@
         <f t="shared" ref="AC6:AM6" si="5">SUM(AC4:AC5)</f>
         <v>10532</v>
       </c>
-      <c r="AD6" s="81">
+      <c r="AD6" s="80">
         <f>SUM(AD4:AD5)</f>
         <v>11186.560000000001</v>
       </c>
@@ -3025,7 +3283,7 @@
       </c>
       <c r="B9" s="9">
         <f>B6-B7+B8</f>
-        <v>43500</v>
+        <v>43000</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>44</v>
@@ -3231,7 +3489,7 @@
         <f t="shared" ref="AC10:AM10" si="10">SUM(AC6:AC9)</f>
         <v>11276</v>
       </c>
-      <c r="AD10" s="81">
+      <c r="AD10" s="80">
         <f t="shared" si="10"/>
         <v>11786.560000000001</v>
       </c>
@@ -3489,7 +3747,7 @@
     </row>
     <row r="13" spans="1:39" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B13" s="26">
         <f>U74/B5</f>
@@ -3701,7 +3959,7 @@
         <f t="shared" ref="AC14:AM14" si="18">SUM(AC10:AC13)</f>
         <v>8518</v>
       </c>
-      <c r="AD14" s="81">
+      <c r="AD14" s="80">
         <f t="shared" si="18"/>
         <v>9000.9800000000014</v>
       </c>
@@ -3744,11 +4002,11 @@
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B15" s="28">
         <f>B4/B13</f>
-        <v>1.5605941020305663</v>
+        <v>1.5426562387888356</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>50</v>
@@ -3956,7 +4214,7 @@
         <f t="shared" ref="AC16:AM16" si="24">SUM(AC14:AC15)</f>
         <v>4738</v>
       </c>
-      <c r="AD16" s="81">
+      <c r="AD16" s="80">
         <f t="shared" si="24"/>
         <v>5348.9800000000014</v>
       </c>
@@ -4189,7 +4447,7 @@
         <f t="shared" ref="AC18:AM18" si="27">SUM(AC16:AC17)</f>
         <v>4610</v>
       </c>
-      <c r="AD18" s="81">
+      <c r="AD18" s="80">
         <f t="shared" si="27"/>
         <v>5220.9800000000014</v>
       </c>
@@ -4437,7 +4695,7 @@
         <f t="shared" ref="AC20:AM20" si="31">SUM(AC18:AC19)</f>
         <v>3611</v>
       </c>
-      <c r="AD20" s="81">
+      <c r="AD20" s="80">
         <f t="shared" si="31"/>
         <v>4176.7840000000015</v>
       </c>
@@ -5417,7 +5675,7 @@
       <c r="B23" s="3"/>
       <c r="AD23" s="3"/>
       <c r="AO23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AP23" s="53">
         <v>0.1</v>
@@ -5433,7 +5691,7 @@
       <c r="F24" s="23"/>
       <c r="G24" s="23"/>
       <c r="H24" s="23" t="e">
-        <f t="shared" ref="H24:R24" si="38">(H10-D10)/D10</f>
+        <f t="shared" ref="H24:T24" si="38">(H10-D10)/D10</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I24" s="23" t="e">
@@ -5477,16 +5735,16 @@
         <v>0.15589051963506545</v>
       </c>
       <c r="S24" s="23">
-        <f>(S10-O10)/O10</f>
+        <f t="shared" si="38"/>
         <v>8.8880624767571581E-2</v>
       </c>
       <c r="T24" s="23">
-        <f>(T10-S10)/S10</f>
-        <v>4.4398907103825134E-3</v>
+        <f t="shared" si="38"/>
+        <v>7.5319926873857398E-2</v>
       </c>
       <c r="U24" s="23">
-        <f>(U10-T10)/T10</f>
-        <v>3.876232573954437E-2</v>
+        <f>(U10-Q10)/Q10</f>
+        <v>0.13190070396443127</v>
       </c>
       <c r="Z24" s="23">
         <f t="shared" ref="Z24:AB24" si="39">(Z10-Y10)/Y10</f>
@@ -5504,7 +5762,7 @@
         <f>(AC10-AB10)/AB10</f>
         <v>0.14083367057871307</v>
       </c>
-      <c r="AD24" s="82">
+      <c r="AD24" s="81">
         <f>(AD10-AC10)/AC10</f>
         <v>4.5278467541681564E-2</v>
       </c>
@@ -5545,7 +5803,7 @@
         <v>9.807164640248954E-2</v>
       </c>
       <c r="AO24" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AP24" s="53">
         <v>-0.01</v>
@@ -5636,7 +5894,7 @@
         <v>-1.2547528517110267E-2</v>
       </c>
       <c r="Z25" s="24">
-        <f t="shared" si="42"/>
+        <f>Z18/Z10</f>
         <v>0.19111302847282141</v>
       </c>
       <c r="AA25" s="24">
@@ -5651,7 +5909,7 @@
         <f>AC18/AC10</f>
         <v>0.40883291947499112</v>
       </c>
-      <c r="AD25" s="83">
+      <c r="AD25" s="82">
         <f>AD18/AD10</f>
         <v>0.44296045665571643</v>
       </c>
@@ -5692,7 +5950,7 @@
         <v>0.48614781395981005</v>
       </c>
       <c r="AO25" s="46" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AP25" s="54">
         <f>NPV(AP23,AD20:HF20)</f>
@@ -5735,7 +5993,7 @@
       <c r="U26" s="24">
         <v>0.13400000000000001</v>
       </c>
-      <c r="AD26" s="83"/>
+      <c r="AD26" s="82"/>
       <c r="AO26" s="24" t="s">
         <v>2</v>
       </c>
@@ -5779,9 +6037,9 @@
       <c r="U27" s="24">
         <v>0.183</v>
       </c>
-      <c r="AD27" s="83"/>
+      <c r="AD27" s="82"/>
       <c r="AO27" s="24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AP27" s="12">
         <f>AP25/AP26</f>
@@ -5795,34 +6053,44 @@
         <v>61</v>
       </c>
       <c r="L28" s="24">
-        <v>8.3000000000000004E-2</v>
+        <f t="shared" ref="L28:Q28" si="43">L6*4/AVERAGE(K47:L47)</f>
+        <v>7.6485309441322369E-2</v>
       </c>
       <c r="M28" s="24">
-        <v>7.8E-2</v>
+        <f t="shared" si="43"/>
+        <v>7.7609516322704936E-2</v>
       </c>
       <c r="N28" s="24">
-        <v>7.9000000000000001E-2</v>
+        <f t="shared" si="43"/>
+        <v>7.9472533375861937E-2</v>
       </c>
       <c r="O28" s="24">
-        <v>8.3000000000000004E-2</v>
+        <f t="shared" si="43"/>
+        <v>8.2557827117070909E-2</v>
       </c>
       <c r="P28" s="24">
-        <v>8.1000000000000003E-2</v>
+        <f t="shared" si="43"/>
+        <v>8.1407148494757026E-2</v>
       </c>
       <c r="Q28" s="24">
-        <v>8.1000000000000003E-2</v>
+        <f t="shared" si="43"/>
+        <v>8.1097956245600497E-2</v>
       </c>
       <c r="R28" s="24">
-        <v>8.4000000000000005E-2</v>
+        <f>R6*4/AVERAGE(Q47:R47)</f>
+        <v>8.3760578170362587E-2</v>
       </c>
       <c r="S28" s="24">
-        <v>8.3000000000000004E-2</v>
+        <f>S6*4/AVERAGE(R47:S47)</f>
+        <v>8.3214556482183469E-2</v>
       </c>
       <c r="T28" s="24">
-        <v>0.08</v>
+        <f>T6*4/AVERAGE(S47:T47)</f>
+        <v>8.0200353565114915E-2</v>
       </c>
       <c r="U28" s="24">
-        <v>8.1000000000000003E-2</v>
+        <f>U6*4/AVERAGE(T47:U47)</f>
+        <v>8.1181621579530447E-2</v>
       </c>
       <c r="V28" s="42"/>
       <c r="W28" s="42"/>
@@ -5831,18 +6099,18 @@
         <v>8.4635310498817715E-2</v>
       </c>
       <c r="AA28" s="42">
-        <f t="shared" ref="AA28:AG28" si="43">AA6/AVERAGE(Z47:AA47)</f>
+        <f t="shared" ref="AA28:AG28" si="44">AA6/AVERAGE(Z47:AA47)</f>
         <v>8.0381341231012135E-2</v>
       </c>
       <c r="AB28" s="42">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>7.925173403135112E-2</v>
       </c>
       <c r="AC28" s="42">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>8.2028435797483534E-2</v>
       </c>
-      <c r="AD28" s="84">
+      <c r="AD28" s="83">
         <f>AD6/AVERAGE(AC47:AD47)</f>
         <v>7.9630995654067324E-2</v>
       </c>
@@ -5851,11 +6119,11 @@
         <v>8.1481067919311256E-2</v>
       </c>
       <c r="AF28" s="42">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>8.1537702564681291E-2</v>
       </c>
       <c r="AG28" s="42">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>8.1273256340428174E-2</v>
       </c>
       <c r="AH28" s="42">
@@ -5863,31 +6131,31 @@
         <v>8.0928419214559011E-2</v>
       </c>
       <c r="AI28" s="42">
-        <f t="shared" ref="AI28:AM28" si="44">AI6/AVERAGE(AH47:AI47)</f>
+        <f t="shared" ref="AI28:AM28" si="45">AI6/AVERAGE(AH47:AI47)</f>
         <v>8.127747488095656E-2</v>
       </c>
       <c r="AJ28" s="42">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.2094680484222846E-2</v>
       </c>
       <c r="AK28" s="42">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.2094680484222846E-2</v>
       </c>
       <c r="AL28" s="42">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.2094680484222846E-2</v>
       </c>
       <c r="AM28" s="42">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.2094680484222846E-2</v>
       </c>
       <c r="AO28" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AP28" s="23">
         <f>(AP27-B4)/B4</f>
-        <v>0.94995579474362812</v>
+        <v>0.97262969933367038</v>
       </c>
     </row>
     <row r="29" spans="1:214" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -5932,11 +6200,11 @@
         <v>0.62737642585551334</v>
       </c>
       <c r="Z29" s="23">
-        <f t="shared" ref="Z29:AM29" si="45">-SUM(Z11:Z13)/Z10</f>
+        <f t="shared" ref="Z29:AM29" si="46">-SUM(Z11:Z13)/Z10</f>
         <v>0.46016681046879493</v>
       </c>
       <c r="AA29" s="23">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.34634834764200872</v>
       </c>
       <c r="AB29" s="23">
@@ -5947,7 +6215,7 @@
         <f>-SUM(AC11:AC13)/AC10</f>
         <v>0.24459028024122029</v>
       </c>
-      <c r="AD29" s="82">
+      <c r="AD29" s="81">
         <f>-SUM(AD11:AD13)/AD10</f>
         <v>0.23633528357722691</v>
       </c>
@@ -5956,35 +6224,35 @@
         <v>0.20704154417710793</v>
       </c>
       <c r="AF29" s="23">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.19098256352876</v>
       </c>
       <c r="AG29" s="23">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.18880137378114603</v>
       </c>
       <c r="AH29" s="23">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.18678001080905265</v>
       </c>
       <c r="AI29" s="23">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.1849042018326259</v>
       </c>
       <c r="AJ29" s="23">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.18351449900748654</v>
       </c>
       <c r="AK29" s="23">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.18388073664163004</v>
       </c>
       <c r="AL29" s="23">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.18422499594261627</v>
       </c>
       <c r="AM29" s="23">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.18454851848765344</v>
       </c>
     </row>
@@ -6025,55 +6293,55 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Z30" s="24">
-        <f t="shared" ref="Z30:AB30" si="46">-Z15/AVERAGE(Y47:Z47)</f>
+        <f>-Z15/AVERAGE(Y47:Z47)</f>
         <v>3.0419538751983541E-2</v>
       </c>
       <c r="AA30" s="24">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="Z30:AB30" si="47">-AA15/AVERAGE(Z47:AA47)</f>
         <v>3.9290616813407279E-2</v>
       </c>
       <c r="AB30" s="24">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>3.5375518504150168E-2</v>
       </c>
       <c r="AC30" s="24">
         <f>-AC15/AVERAGE(AB47:AC47)</f>
         <v>2.9440513417630817E-2</v>
       </c>
-      <c r="AD30" s="83">
+      <c r="AD30" s="82">
         <f>-AD15/AVERAGE(AC47:AD47)</f>
         <v>2.5996588417588059E-2</v>
       </c>
       <c r="AE30" s="24">
-        <f t="shared" ref="AE30:AL30" si="47">-AE15/AVERAGE(AD47:AE47)</f>
+        <f t="shared" ref="AE30:AL30" si="48">-AE15/AVERAGE(AD47:AE47)</f>
         <v>2.665928980330665E-2</v>
       </c>
       <c r="AF30" s="24">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2.737337792303807E-2</v>
       </c>
       <c r="AG30" s="24">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2.7373377923038074E-2</v>
       </c>
       <c r="AH30" s="24">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2.7128972763010944E-2</v>
       </c>
       <c r="AI30" s="24">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2.714281407564513E-2</v>
       </c>
       <c r="AJ30" s="24">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2.7389566930878271E-2</v>
       </c>
       <c r="AK30" s="24">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2.7389566930878267E-2</v>
       </c>
       <c r="AL30" s="24">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>2.7389566930878267E-2</v>
       </c>
       <c r="AM30" s="24">
@@ -6132,48 +6400,48 @@
       <c r="AC31" s="24">
         <v>0.24199999999999999</v>
       </c>
-      <c r="AD31" s="83"/>
+      <c r="AD31" s="82"/>
     </row>
     <row r="32" spans="1:214" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L32" s="24">
-        <f t="shared" ref="L32:T32" si="48">(L20*4)/AVERAGE(K74:L74)</f>
+        <f t="shared" ref="L32:T32" si="49">(L20*4)/AVERAGE(K74:L74)</f>
         <v>7.881102381357788E-2</v>
       </c>
       <c r="M32" s="24">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.10800205540243846</v>
       </c>
       <c r="N32" s="24">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.1089654226752291</v>
       </c>
       <c r="O32" s="24">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11139670548266691</v>
       </c>
       <c r="P32" s="24">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.14289133036005655</v>
       </c>
       <c r="Q32" s="24">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.14958977294409465</v>
       </c>
       <c r="R32" s="24">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.14850407605905666</v>
       </c>
       <c r="S32" s="24">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.15727432935187</v>
       </c>
       <c r="T32" s="24">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.14877994511607209</v>
       </c>
       <c r="U32" s="24">
@@ -6181,38 +6449,38 @@
         <v>0.15970334635393227</v>
       </c>
       <c r="Y32" s="24">
-        <f t="shared" ref="Y32:AB32" si="49">Y20/Y74</f>
+        <f t="shared" ref="Y32:AB32" si="50">Y20/Y74</f>
         <v>-1.2135282013401572E-3</v>
       </c>
       <c r="Z32" s="24">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>4.9255846917080084E-2</v>
       </c>
       <c r="AA32" s="24">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>5.9376719523785704E-2</v>
       </c>
       <c r="AB32" s="24">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>9.7098509568745037E-2</v>
       </c>
       <c r="AC32" s="24">
         <f>AC20/AC74</f>
         <v>0.13754618519788214</v>
       </c>
-      <c r="AD32" s="83"/>
+      <c r="AD32" s="82"/>
     </row>
     <row r="33" spans="1:39" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="13"/>
-      <c r="AD33" s="83"/>
+      <c r="AD33" s="82"/>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A34" s="15"/>
       <c r="B34" s="18"/>
       <c r="C34" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D34" s="15"/>
       <c r="E34" s="15"/>
@@ -6280,10 +6548,10 @@
       <c r="A35" s="6"/>
       <c r="B35" s="25"/>
       <c r="C35" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K35" s="51">
-        <f t="shared" ref="K35:T35" si="50">(K34-G34)/G34</f>
+        <f t="shared" ref="K35:T35" si="51">(K34-G34)/G34</f>
         <v>0.23184067015235846</v>
       </c>
       <c r="M35" s="51">
@@ -6291,31 +6559,31 @@
         <v>0.15257068613499969</v>
       </c>
       <c r="N35" s="51">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.13126718849164376</v>
       </c>
       <c r="O35" s="51">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.1329598484762046</v>
       </c>
       <c r="P35" s="51">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>6.6301796564810139E-2</v>
       </c>
       <c r="Q35" s="51">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>8.3021096140426215E-2</v>
       </c>
       <c r="R35" s="51">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>7.6110331930808794E-2</v>
       </c>
       <c r="S35" s="51">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>4.976031260070899E-2</v>
       </c>
       <c r="T35" s="51">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.12847282938520249</v>
       </c>
       <c r="U35" s="51">
@@ -6334,52 +6602,52 @@
         <f>(AC34-AB34)/AB34</f>
         <v>4.976031260070899E-2</v>
       </c>
-      <c r="AD35" s="85"/>
+      <c r="AD35" s="84"/>
     </row>
     <row r="36" spans="1:39" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
       <c r="B36" s="25"/>
       <c r="C36" s="19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K36" s="51">
-        <f t="shared" ref="K36:T36" si="51">K34/K47</f>
+        <f t="shared" ref="K36:T36" si="52">K34/K47</f>
         <v>0.79587907846823036</v>
       </c>
       <c r="L36" s="51">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.79666215212547509</v>
       </c>
       <c r="M36" s="51">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.79561470193810702</v>
       </c>
       <c r="N36" s="51">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.79419627386590541</v>
       </c>
       <c r="O36" s="51">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.79789148881460525</v>
       </c>
       <c r="P36" s="51">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.78475832230150788</v>
       </c>
       <c r="Q36" s="51">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.79079684866538624</v>
       </c>
       <c r="R36" s="51">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.78793388052548707</v>
       </c>
       <c r="S36" s="51">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.78763950703107877</v>
       </c>
       <c r="T36" s="51">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.78825828609201098</v>
       </c>
       <c r="U36" s="51">
@@ -6387,53 +6655,53 @@
         <v>0.78677065602589502</v>
       </c>
       <c r="AA36" s="51">
-        <f t="shared" ref="AA36:AB36" si="52">AA34/AA47</f>
+        <f t="shared" ref="AA36:AB36" si="53">AA34/AA47</f>
         <v>0.79587907846823036</v>
       </c>
       <c r="AB36" s="51">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.79789148881460525</v>
       </c>
       <c r="AC36" s="51">
         <f>AC34/AC47</f>
         <v>0.78763950703107877</v>
       </c>
-      <c r="AD36" s="85"/>
+      <c r="AD36" s="84"/>
     </row>
     <row r="37" spans="1:39" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="13"/>
-      <c r="AD37" s="83"/>
+      <c r="AD37" s="82"/>
     </row>
     <row r="38" spans="1:39" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K38" s="24">
-        <f t="shared" ref="K38:R38" si="53">(K15-G15)/G15</f>
+        <f t="shared" ref="K38:R38" si="54">(K15-G15)/G15</f>
         <v>0.33216374269005849</v>
       </c>
       <c r="N38" s="24">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>-0.10859728506787331</v>
       </c>
       <c r="O38" s="24">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>1.7559262510974539E-3</v>
       </c>
       <c r="P38" s="24">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>-6.2328139321723187E-2</v>
       </c>
       <c r="Q38" s="24">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>-2.4678111587982832E-2</v>
       </c>
       <c r="R38" s="24">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>-6.8020304568527923E-2</v>
       </c>
       <c r="S38" s="24">
@@ -6448,42 +6716,42 @@
         <f>(U15-Q15)/Q15</f>
         <v>-2.8602860286028604E-2</v>
       </c>
-      <c r="AD38" s="83"/>
+      <c r="AD38" s="82"/>
     </row>
     <row r="39" spans="1:39" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="13"/>
-      <c r="AD39" s="83"/>
+      <c r="AD39" s="82"/>
     </row>
     <row r="40" spans="1:39" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O40" s="24">
-        <f t="shared" ref="O40:T40" si="54">(O47-K47)/K47</f>
+        <f t="shared" ref="O40:T40" si="55">(O47-K47)/K47</f>
         <v>0.13010234196928833</v>
       </c>
       <c r="P40" s="24">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>8.2476298658744382E-2</v>
       </c>
       <c r="Q40" s="24">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>8.9619297361475322E-2</v>
       </c>
       <c r="R40" s="24">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>8.4663113252693933E-2</v>
       </c>
       <c r="S40" s="24">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>6.3424080740550268E-2</v>
       </c>
       <c r="T40" s="24">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.12346227115688871</v>
       </c>
       <c r="U40" s="24">
@@ -6491,59 +6759,59 @@
         <v>0.12372515972249441</v>
       </c>
       <c r="Z40" s="24">
-        <f t="shared" ref="Z40:AB40" si="55">(Z47-Y47)/Y47</f>
+        <f t="shared" ref="Z40:AB40" si="56">(Z47-Y47)/Y47</f>
         <v>0.25572643284616797</v>
       </c>
       <c r="AA40" s="24">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.24071612060029746</v>
       </c>
       <c r="AB40" s="24">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.13010234196928833</v>
       </c>
       <c r="AC40" s="24">
         <f>(AC47-AB47)/AB47</f>
         <v>6.3424080740550268E-2</v>
       </c>
-      <c r="AD40" s="83">
-        <f t="shared" ref="AD40:AM40" si="56">(AD47-AC47)/AC47</f>
+      <c r="AD40" s="82">
+        <f t="shared" ref="AD40:AM40" si="57">(AD47-AC47)/AC47</f>
         <v>0.123</v>
       </c>
       <c r="AE40" s="24">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.12000000000000008</v>
       </c>
       <c r="AF40" s="24">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.12000000000000018</v>
       </c>
       <c r="AG40" s="24">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.12000000000000008</v>
       </c>
       <c r="AH40" s="24">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.12000000000000012</v>
       </c>
       <c r="AI40" s="24">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.1000000000000001</v>
       </c>
       <c r="AJ40" s="24">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.10000000000000014</v>
       </c>
       <c r="AK40" s="24">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.10000000000000012</v>
       </c>
       <c r="AL40" s="24">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.10000000000000003</v>
       </c>
       <c r="AM40" s="24">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.1000000000000001</v>
       </c>
     </row>
@@ -6551,7 +6819,7 @@
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="13"/>
-      <c r="AD41" s="83"/>
+      <c r="AD41" s="82"/>
     </row>
     <row r="42" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="3"/>
@@ -6846,15 +7114,15 @@
         <v>166453.21616000001</v>
       </c>
       <c r="AF47" s="15">
-        <f t="shared" ref="AF47:AH47" si="57">AE47*1.12</f>
+        <f t="shared" ref="AF47:AH47" si="58">AE47*1.12</f>
         <v>186427.60209920004</v>
       </c>
       <c r="AG47" s="15">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>208798.91435110406</v>
       </c>
       <c r="AH47" s="15">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>233854.78407323657</v>
       </c>
       <c r="AI47" s="15">
@@ -6862,19 +7130,19 @@
         <v>257240.26248056025</v>
       </c>
       <c r="AJ47" s="15">
-        <f t="shared" ref="AJ47:AM47" si="58">AI47*1.1</f>
+        <f t="shared" ref="AJ47:AM47" si="59">AI47*1.1</f>
         <v>282964.28872861632</v>
       </c>
       <c r="AK47" s="15">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>311260.71760147798</v>
       </c>
       <c r="AL47" s="15">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>342386.78936162579</v>
       </c>
       <c r="AM47" s="15">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>376625.46829778841</v>
       </c>
     </row>
@@ -7437,66 +7705,66 @@
         <v>80</v>
       </c>
       <c r="D57" s="16">
-        <f t="shared" ref="D57:S57" si="59">SUM(D44:D56)</f>
+        <f t="shared" ref="D57:S57" si="60">SUM(D44:D56)</f>
         <v>0</v>
       </c>
       <c r="E57" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="F57" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="G57" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="H57" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="I57" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="J57" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K57" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>138065</v>
       </c>
       <c r="L57" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>148135</v>
       </c>
       <c r="M57" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>149026</v>
       </c>
       <c r="N57" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>150750</v>
       </c>
       <c r="O57" s="16">
         <v>159143</v>
       </c>
       <c r="P57" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>158437</v>
       </c>
       <c r="Q57" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>162605</v>
       </c>
       <c r="R57" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>166579</v>
       </c>
       <c r="S57" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>162910</v>
       </c>
       <c r="T57" s="16">
@@ -7523,7 +7791,7 @@
       <c r="AC57" s="16">
         <v>162909</v>
       </c>
-      <c r="AD57" s="81"/>
+      <c r="AD57" s="80"/>
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.25">
       <c r="C58" s="2" t="s">
@@ -7652,7 +7920,7 @@
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.25">
       <c r="C60" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D60" s="15"/>
       <c r="E60" s="15"/>
@@ -7714,7 +7982,7 @@
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.25">
       <c r="C61" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D61" s="15"/>
       <c r="E61" s="15"/>
@@ -8091,66 +8359,66 @@
         <v>88</v>
       </c>
       <c r="D67" s="17">
-        <f t="shared" ref="D67:S67" si="60">SUM(D58:D66)</f>
+        <f t="shared" ref="D67:S67" si="61">SUM(D58:D66)</f>
         <v>0</v>
       </c>
       <c r="E67" s="17">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="F67" s="17">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="G67" s="17">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="H67" s="17">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="I67" s="17">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="J67" s="17">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="K67" s="17">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>118074</v>
       </c>
       <c r="L67" s="17">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>127012</v>
       </c>
       <c r="M67" s="17">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>127331</v>
       </c>
       <c r="N67" s="17">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>128690</v>
       </c>
       <c r="O67" s="17">
         <v>136465</v>
       </c>
       <c r="P67" s="17">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>135149</v>
       </c>
       <c r="Q67" s="17">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>138724</v>
       </c>
       <c r="R67" s="17">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>141763</v>
       </c>
       <c r="S67" s="17">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>136656</v>
       </c>
       <c r="T67" s="17">
@@ -8177,7 +8445,7 @@
       <c r="AC67" s="17">
         <v>136656</v>
       </c>
-      <c r="AD67" s="86"/>
+      <c r="AD67" s="85"/>
     </row>
     <row r="68" spans="1:31" x14ac:dyDescent="0.25">
       <c r="C68" s="2" t="s">
@@ -8552,63 +8820,63 @@
         <v>95</v>
       </c>
       <c r="D74" s="17">
-        <f t="shared" ref="D74:R74" si="61">SUM(D68:D73)</f>
+        <f t="shared" ref="D74:R74" si="62">SUM(D68:D73)</f>
         <v>0</v>
       </c>
       <c r="E74" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="F74" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="G74" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="H74" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="I74" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="J74" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="K74" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>19991</v>
       </c>
       <c r="L74" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>21120</v>
       </c>
       <c r="M74" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>21694</v>
       </c>
       <c r="N74" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>22063</v>
       </c>
       <c r="O74" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>22678</v>
       </c>
       <c r="P74" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>23287</v>
       </c>
       <c r="Q74" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>23882</v>
       </c>
       <c r="R74" s="17">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>24817</v>
       </c>
       <c r="S74" s="17">
@@ -8624,10 +8892,7 @@
         <v>27874</v>
       </c>
       <c r="V74" s="29"/>
-      <c r="W74" s="29">
-        <f>U74-U51</f>
-        <v>19662</v>
-      </c>
+      <c r="W74" s="29"/>
       <c r="X74" s="5"/>
       <c r="Y74" s="17">
         <v>18953</v>
@@ -8644,7 +8909,7 @@
       <c r="AC74" s="17">
         <v>26253</v>
       </c>
-      <c r="AD74" s="86"/>
+      <c r="AD74" s="85"/>
     </row>
     <row r="75" spans="1:31" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
@@ -8653,63 +8918,63 @@
         <v>96</v>
       </c>
       <c r="D75" s="16">
-        <f t="shared" ref="D75:R75" si="62">D67+D74</f>
+        <f t="shared" ref="D75:R75" si="63">D67+D74</f>
         <v>0</v>
       </c>
       <c r="E75" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="F75" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="G75" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="H75" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="I75" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="J75" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K75" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>138065</v>
       </c>
       <c r="L75" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>148132</v>
       </c>
       <c r="M75" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>149025</v>
       </c>
       <c r="N75" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>150753</v>
       </c>
       <c r="O75" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>159143</v>
       </c>
       <c r="P75" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>158436</v>
       </c>
       <c r="Q75" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>162606</v>
       </c>
       <c r="R75" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>166580</v>
       </c>
       <c r="S75" s="16">
@@ -8745,7 +9010,7 @@
         <f>AC67+AC74</f>
         <v>162909</v>
       </c>
-      <c r="AD75" s="81"/>
+      <c r="AD75" s="80"/>
     </row>
     <row r="76" spans="1:31" x14ac:dyDescent="0.25">
       <c r="D76" s="15"/>
@@ -8781,7 +9046,7 @@
       <c r="C77" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AD77" s="87"/>
+      <c r="AD77" s="86"/>
       <c r="AE77" s="31"/>
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.25">
@@ -8793,63 +9058,63 @@
         <v>0</v>
       </c>
       <c r="E78" s="15">
-        <f t="shared" ref="E78:S78" si="63">E18</f>
+        <f t="shared" ref="E78:S78" si="64">E18</f>
         <v>0</v>
       </c>
       <c r="F78" s="15">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="G78" s="15">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>77</v>
       </c>
       <c r="H78" s="15">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="I78" s="15">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="J78" s="15">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>373</v>
       </c>
       <c r="K78" s="15">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>249</v>
       </c>
       <c r="L78" s="15">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>535</v>
       </c>
       <c r="M78" s="15">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>765</v>
       </c>
       <c r="N78" s="15">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>807</v>
       </c>
       <c r="O78" s="15">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>771</v>
       </c>
       <c r="P78" s="15">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1049</v>
       </c>
       <c r="Q78" s="15">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1130</v>
       </c>
       <c r="R78" s="15">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1161</v>
       </c>
       <c r="S78" s="15">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1270</v>
       </c>
       <c r="T78" s="15">
@@ -8863,23 +9128,23 @@
       <c r="V78" s="15"/>
       <c r="W78" s="15"/>
       <c r="Y78" s="15">
-        <f t="shared" ref="Y78:AC78" si="64">Y18</f>
+        <f t="shared" ref="Y78:AC78" si="65">Y18</f>
         <v>-33</v>
       </c>
       <c r="Z78" s="15">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>1329</v>
       </c>
       <c r="AA78" s="15">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>1515</v>
       </c>
       <c r="AB78" s="15">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>2878</v>
       </c>
       <c r="AC78" s="15">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>4610</v>
       </c>
     </row>
@@ -9138,63 +9403,63 @@
         <v>0</v>
       </c>
       <c r="E83" s="16">
-        <f t="shared" ref="E83:S83" si="65">SUM(E79:E82)</f>
+        <f t="shared" ref="E83:S83" si="66">SUM(E79:E82)</f>
         <v>0</v>
       </c>
       <c r="F83" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="G83" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="H83" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="I83" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="J83" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="K83" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="L83" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>-823</v>
       </c>
       <c r="M83" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>1122</v>
       </c>
       <c r="N83" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>-1123</v>
       </c>
       <c r="O83" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>7674</v>
       </c>
       <c r="P83" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>-4667</v>
       </c>
       <c r="Q83" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>967</v>
       </c>
       <c r="R83" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>-745</v>
       </c>
       <c r="S83" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>-1610</v>
       </c>
       <c r="T83" s="16">
@@ -9207,26 +9472,26 @@
       </c>
       <c r="X83" s="1"/>
       <c r="Y83" s="16">
-        <f t="shared" ref="Y83" si="66">SUM(Y79:Y82)</f>
+        <f t="shared" ref="Y83" si="67">SUM(Y79:Y82)</f>
         <v>465</v>
       </c>
       <c r="Z83" s="16">
-        <f t="shared" ref="Z83" si="67">SUM(Z79:Z82)</f>
+        <f t="shared" ref="Z83" si="68">SUM(Z79:Z82)</f>
         <v>-8511</v>
       </c>
       <c r="AA83" s="16">
-        <f t="shared" ref="AA83" si="68">SUM(AA79:AA82)</f>
+        <f t="shared" ref="AA83" si="69">SUM(AA79:AA82)</f>
         <v>-2680</v>
       </c>
       <c r="AB83" s="16">
-        <f t="shared" ref="AB83" si="69">SUM(AB79:AB82)</f>
+        <f t="shared" ref="AB83" si="70">SUM(AB79:AB82)</f>
         <v>6850</v>
       </c>
       <c r="AC83" s="16">
-        <f t="shared" ref="AC83" si="70">SUM(AC79:AC82)</f>
+        <f t="shared" ref="AC83" si="71">SUM(AC79:AC82)</f>
         <v>-6055</v>
       </c>
-      <c r="AD83" s="81"/>
+      <c r="AD83" s="80"/>
     </row>
     <row r="84" spans="1:30" x14ac:dyDescent="0.25">
       <c r="D84" s="15"/>
@@ -9293,7 +9558,7 @@
     </row>
     <row r="86" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C86" s="2" t="s">
-        <v>105</v>
+        <v>244</v>
       </c>
       <c r="D86" s="15"/>
       <c r="E86" s="15"/>
@@ -9356,70 +9621,70 @@
       <c r="A87" s="1"/>
       <c r="B87" s="20"/>
       <c r="C87" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D87" s="16">
         <f>SUM(D85:D86)</f>
         <v>0</v>
       </c>
       <c r="E87" s="16">
-        <f t="shared" ref="E87:S87" si="71">SUM(E85:E86)</f>
+        <f t="shared" ref="E87:S87" si="72">SUM(E85:E86)</f>
         <v>0</v>
       </c>
       <c r="F87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="G87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="H87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="I87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="J87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="L87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>-17</v>
       </c>
       <c r="M87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>-21</v>
       </c>
       <c r="N87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>-67</v>
       </c>
       <c r="O87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>-29</v>
       </c>
       <c r="P87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>-52</v>
       </c>
       <c r="Q87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>-64</v>
       </c>
       <c r="R87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>-39</v>
       </c>
       <c r="S87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>-26</v>
       </c>
       <c r="T87" s="16">
@@ -9432,26 +9697,26 @@
       </c>
       <c r="X87" s="1"/>
       <c r="Y87" s="16">
-        <f t="shared" ref="Y87" si="72">SUM(Y85:Y86)</f>
+        <f t="shared" ref="Y87" si="73">SUM(Y85:Y86)</f>
         <v>-14106</v>
       </c>
       <c r="Z87" s="16">
-        <f t="shared" ref="Z87" si="73">SUM(Z85:Z86)</f>
+        <f t="shared" ref="Z87" si="74">SUM(Z85:Z86)</f>
         <v>10260</v>
       </c>
       <c r="AA87" s="16">
-        <f t="shared" ref="AA87" si="74">SUM(AA85:AA86)</f>
+        <f t="shared" ref="AA87" si="75">SUM(AA85:AA86)</f>
         <v>-75</v>
       </c>
       <c r="AB87" s="16">
-        <f t="shared" ref="AB87" si="75">SUM(AB85:AB86)</f>
+        <f t="shared" ref="AB87" si="76">SUM(AB85:AB86)</f>
         <v>-134</v>
       </c>
       <c r="AC87" s="16">
-        <f t="shared" ref="AC87" si="76">SUM(AC85:AC86)</f>
+        <f t="shared" ref="AC87" si="77">SUM(AC85:AC86)</f>
         <v>-181</v>
       </c>
-      <c r="AD87" s="81"/>
+      <c r="AD87" s="80"/>
     </row>
     <row r="88" spans="1:30" x14ac:dyDescent="0.25">
       <c r="D88" s="15"/>
@@ -9477,7 +9742,7 @@
     </row>
     <row r="89" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C89" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D89" s="15">
         <v>0</v>
@@ -9538,7 +9803,7 @@
     </row>
     <row r="90" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C90" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D90" s="15"/>
       <c r="E90" s="15"/>
@@ -9598,7 +9863,7 @@
     </row>
     <row r="91" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C91" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D91" s="15"/>
       <c r="E91" s="15"/>
@@ -9658,7 +9923,7 @@
     </row>
     <row r="92" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C92" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D92" s="15"/>
       <c r="E92" s="15"/>
@@ -9719,7 +9984,7 @@
     </row>
     <row r="93" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C93" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D93" s="15"/>
       <c r="E93" s="15"/>
@@ -9780,7 +10045,7 @@
     </row>
     <row r="94" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C94" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D94" s="15"/>
       <c r="E94" s="15"/>
@@ -9841,7 +10106,7 @@
     </row>
     <row r="95" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C95" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D95" s="15"/>
       <c r="E95" s="15"/>
@@ -9904,70 +10169,70 @@
       <c r="A96" s="1"/>
       <c r="B96" s="20"/>
       <c r="C96" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D96" s="16">
         <f>SUM(D90:D95)</f>
         <v>0</v>
       </c>
       <c r="E96" s="16">
-        <f t="shared" ref="E96:S96" si="77">SUM(E90:E95)</f>
+        <f t="shared" ref="E96:S96" si="78">SUM(E90:E95)</f>
         <v>0</v>
       </c>
       <c r="F96" s="16">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="G96" s="16">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="H96" s="16">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="I96" s="16">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="J96" s="16">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="K96" s="16">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="L96" s="16">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1228</v>
       </c>
       <c r="M96" s="16">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>-425</v>
       </c>
       <c r="N96" s="16">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>-57</v>
       </c>
       <c r="O96" s="16">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>-56</v>
       </c>
       <c r="P96" s="16">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>-51</v>
       </c>
       <c r="Q96" s="16">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>-49</v>
       </c>
       <c r="R96" s="16">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>-48</v>
       </c>
       <c r="S96" s="16">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>756</v>
       </c>
       <c r="T96" s="16">
@@ -9984,22 +10249,22 @@
         <v>16750</v>
       </c>
       <c r="Z96" s="16">
-        <f t="shared" ref="Z96:AC96" si="78">SUM(Z89:Z95)</f>
+        <f t="shared" ref="Z96:AC96" si="79">SUM(Z89:Z95)</f>
         <v>131</v>
       </c>
       <c r="AA96" s="16">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>-56</v>
       </c>
       <c r="AB96" s="16">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>690</v>
       </c>
       <c r="AC96" s="16">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>608</v>
       </c>
-      <c r="AD96" s="81"/>
+      <c r="AD96" s="80"/>
     </row>
     <row r="97" spans="3:29" x14ac:dyDescent="0.25">
       <c r="T97" s="15"/>
@@ -10012,7 +10277,7 @@
     </row>
     <row r="98" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C98" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L98" s="2">
         <v>124</v>
@@ -10076,66 +10341,66 @@
     </row>
     <row r="100" spans="3:29" x14ac:dyDescent="0.25">
       <c r="C100" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D100" s="15">
         <f>D83+D87+D96</f>
         <v>0</v>
       </c>
       <c r="E100" s="15">
-        <f t="shared" ref="E100:R100" si="79">E83+E87+E96</f>
+        <f t="shared" ref="E100:R100" si="80">E83+E87+E96</f>
         <v>0</v>
       </c>
       <c r="F100" s="15">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="G100" s="15">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="H100" s="15">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="I100" s="15">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="J100" s="15">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="K100" s="15">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L100" s="15">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>388</v>
       </c>
       <c r="M100" s="15">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>676</v>
       </c>
       <c r="N100" s="15">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>-1247</v>
       </c>
       <c r="O100" s="15">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>7589</v>
       </c>
       <c r="P100" s="15">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>-4770</v>
       </c>
       <c r="Q100" s="15">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>854</v>
       </c>
       <c r="R100" s="15">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>-832</v>
       </c>
       <c r="S100" s="15">
@@ -10153,23 +10418,23 @@
       <c r="V100" s="15"/>
       <c r="W100" s="15"/>
       <c r="Y100" s="15">
-        <f t="shared" ref="Y100:AC100" si="80">Y83+Y87+Y96</f>
+        <f t="shared" ref="Y100:AC100" si="81">Y83+Y87+Y96</f>
         <v>3109</v>
       </c>
       <c r="Z100" s="15">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>1880</v>
       </c>
       <c r="AA100" s="15">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>-2811</v>
       </c>
       <c r="AB100" s="15">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>7406</v>
       </c>
       <c r="AC100" s="15">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>-5628</v>
       </c>
     </row>
@@ -10289,7 +10554,7 @@
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="Z28:AC28 Z30:AA30 AB30:AC30" formulaRange="1"/>
+    <ignoredError sqref="Z28:AC28 AA30 AB30:AC30 P28:R28 L28:O28 T28" formulaRange="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -10371,16 +10636,16 @@
         <v>2025</v>
       </c>
       <c r="W4" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="X4" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="Y4" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Z4" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="Z4" s="4" t="s">
-        <v>120</v>
       </c>
       <c r="AA4" s="41">
         <v>2026</v>
@@ -10388,7 +10653,7 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G5" s="35"/>
       <c r="H5" s="1"/>
@@ -10400,7 +10665,7 @@
     </row>
     <row r="6" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -10452,7 +10717,7 @@
     </row>
     <row r="7" spans="1:27" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G7" s="36"/>
       <c r="H7" s="24" t="e">
@@ -10518,7 +10783,7 @@
     </row>
     <row r="8" spans="1:27" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G8" s="36"/>
       <c r="J8" s="24">
@@ -10564,7 +10829,7 @@
     </row>
     <row r="9" spans="1:27" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G9" s="36"/>
       <c r="J9" s="24">
@@ -10610,7 +10875,7 @@
     </row>
     <row r="10" spans="1:27" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G10" s="37"/>
       <c r="H10" s="16"/>
@@ -10667,7 +10932,7 @@
     <row r="11" spans="1:27" s="32" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="24"/>
       <c r="B11" s="32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G11" s="38"/>
       <c r="J11" s="32">
@@ -10713,7 +10978,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
@@ -10738,7 +11003,7 @@
     </row>
     <row r="13" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
@@ -10790,7 +11055,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -10863,7 +11128,7 @@
     <row r="15" spans="1:27" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C15" s="24"/>
       <c r="D15" s="24"/>
@@ -10916,7 +11181,7 @@
     <row r="16" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C16" s="24"/>
       <c r="D16" s="24"/>
@@ -10968,7 +11233,7 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G17" s="35"/>
       <c r="H17" s="1"/>
@@ -11025,7 +11290,7 @@
     <row r="18" spans="1:27" s="32" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="24"/>
       <c r="B18" s="32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G18" s="38"/>
       <c r="J18" s="32">
@@ -11071,7 +11336,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
@@ -11096,7 +11361,7 @@
     </row>
     <row r="20" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C20" s="16"/>
       <c r="D20" s="16"/>
@@ -11148,7 +11413,7 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
@@ -11221,7 +11486,7 @@
     <row r="22" spans="1:27" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C22" s="24"/>
       <c r="D22" s="24"/>
@@ -11274,7 +11539,7 @@
     <row r="23" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C23" s="24"/>
       <c r="D23" s="24"/>
@@ -11326,7 +11591,7 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G24" s="35"/>
       <c r="H24" s="1"/>
@@ -11383,7 +11648,7 @@
     <row r="25" spans="1:27" s="32" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="24"/>
       <c r="B25" s="32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G25" s="38"/>
       <c r="J25" s="32">
@@ -11503,6 +11768,4082 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D40B97C-8DA9-5F4D-9551-FF3F2010F868}">
+  <dimension ref="B4:AA78"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="15"/>
+    <col min="2" max="2" width="29.5" style="15" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B4" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="87" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="87" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="87" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="87" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="88">
+        <v>2022</v>
+      </c>
+      <c r="H4" s="87" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="87" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="87" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="87" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="88">
+        <v>2023</v>
+      </c>
+      <c r="M4" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="87" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="88">
+        <v>2024</v>
+      </c>
+      <c r="R4" s="87" t="s">
+        <v>31</v>
+      </c>
+      <c r="S4" s="87" t="s">
+        <v>28</v>
+      </c>
+      <c r="T4" s="87" t="s">
+        <v>29</v>
+      </c>
+      <c r="U4" s="87" t="s">
+        <v>30</v>
+      </c>
+      <c r="V4" s="88">
+        <v>2025</v>
+      </c>
+      <c r="W4" s="87" t="s">
+        <v>116</v>
+      </c>
+      <c r="X4" s="87" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y4" s="87" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z4" s="87" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA4" s="39">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B5" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q5" s="37"/>
+      <c r="V5" s="37"/>
+      <c r="AA5" s="37"/>
+    </row>
+    <row r="6" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B6" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="15">
+        <v>1960</v>
+      </c>
+      <c r="J6" s="15">
+        <v>2234</v>
+      </c>
+      <c r="M6" s="15">
+        <v>2425</v>
+      </c>
+      <c r="N6" s="15">
+        <v>2526</v>
+      </c>
+      <c r="O6" s="15">
+        <v>2618</v>
+      </c>
+      <c r="P6" s="15">
+        <v>2688</v>
+      </c>
+      <c r="Q6" s="37">
+        <f>SUM(M6:P6)</f>
+        <v>10257</v>
+      </c>
+      <c r="R6" s="15">
+        <v>2614</v>
+      </c>
+      <c r="S6" s="15">
+        <v>2540</v>
+      </c>
+      <c r="T6" s="15">
+        <v>2651</v>
+      </c>
+      <c r="U6" s="15">
+        <v>2636</v>
+      </c>
+      <c r="V6" s="37">
+        <f>SUM(R6:U6)</f>
+        <v>10441</v>
+      </c>
+      <c r="W6" s="15">
+        <v>2624</v>
+      </c>
+      <c r="X6" s="15">
+        <v>2784</v>
+      </c>
+      <c r="AA6" s="37">
+        <f>SUM(W6:Z6)</f>
+        <v>5408</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B7" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="I7" s="15">
+        <v>-530</v>
+      </c>
+      <c r="J7" s="15">
+        <v>-701</v>
+      </c>
+      <c r="M7" s="15">
+        <v>-836</v>
+      </c>
+      <c r="N7" s="15">
+        <v>-866</v>
+      </c>
+      <c r="O7" s="15">
+        <v>-868</v>
+      </c>
+      <c r="P7" s="15">
+        <v>-828</v>
+      </c>
+      <c r="Q7" s="37">
+        <f>SUM(M7:P7)</f>
+        <v>-3398</v>
+      </c>
+      <c r="R7" s="15">
+        <v>-748</v>
+      </c>
+      <c r="S7" s="15">
+        <v>-666</v>
+      </c>
+      <c r="T7" s="15">
+        <v>-639</v>
+      </c>
+      <c r="U7" s="15">
+        <v>-618</v>
+      </c>
+      <c r="V7" s="37">
+        <f>SUM(R7:U7)</f>
+        <v>-2671</v>
+      </c>
+      <c r="W7" s="15">
+        <v>-621</v>
+      </c>
+      <c r="X7" s="15">
+        <v>-668</v>
+      </c>
+      <c r="AA7" s="37">
+        <f>SUM(W7:Z7)</f>
+        <v>-1289</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="16">
+        <f t="shared" ref="C8:W8" si="0">SUM(C6:C7)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="16">
+        <f t="shared" si="0"/>
+        <v>1430</v>
+      </c>
+      <c r="J8" s="16">
+        <f t="shared" si="0"/>
+        <v>1533</v>
+      </c>
+      <c r="K8" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="16">
+        <f t="shared" si="0"/>
+        <v>1589</v>
+      </c>
+      <c r="N8" s="16">
+        <f t="shared" si="0"/>
+        <v>1660</v>
+      </c>
+      <c r="O8" s="16">
+        <f t="shared" si="0"/>
+        <v>1750</v>
+      </c>
+      <c r="P8" s="16">
+        <f t="shared" si="0"/>
+        <v>1860</v>
+      </c>
+      <c r="Q8" s="39">
+        <f t="shared" si="0"/>
+        <v>6859</v>
+      </c>
+      <c r="R8" s="16">
+        <f t="shared" si="0"/>
+        <v>1866</v>
+      </c>
+      <c r="S8" s="16">
+        <f t="shared" si="0"/>
+        <v>1874</v>
+      </c>
+      <c r="T8" s="16">
+        <f t="shared" si="0"/>
+        <v>2012</v>
+      </c>
+      <c r="U8" s="16">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
+      <c r="V8" s="39">
+        <f t="shared" si="0"/>
+        <v>7770</v>
+      </c>
+      <c r="W8" s="16">
+        <f t="shared" si="0"/>
+        <v>2003</v>
+      </c>
+      <c r="X8" s="16">
+        <f>SUM(X6:X7)</f>
+        <v>2116</v>
+      </c>
+      <c r="Y8" s="16">
+        <f t="shared" ref="Y8:AA8" si="1">SUM(Y6:Y7)</f>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA8" s="39">
+        <f t="shared" si="1"/>
+        <v>4119</v>
+      </c>
+    </row>
+    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B9" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="15">
+        <v>52</v>
+      </c>
+      <c r="J9" s="15">
+        <v>58</v>
+      </c>
+      <c r="M9" s="15">
+        <v>65</v>
+      </c>
+      <c r="N9" s="15">
+        <v>71</v>
+      </c>
+      <c r="O9" s="15">
+        <v>64</v>
+      </c>
+      <c r="P9" s="15">
+        <v>73</v>
+      </c>
+      <c r="Q9" s="37">
+        <f>SUM(M9:P9)</f>
+        <v>273</v>
+      </c>
+      <c r="R9" s="15">
+        <v>86</v>
+      </c>
+      <c r="S9" s="15">
+        <v>70</v>
+      </c>
+      <c r="T9" s="15">
+        <v>75</v>
+      </c>
+      <c r="U9" s="15">
+        <v>99</v>
+      </c>
+      <c r="V9" s="37">
+        <f>SUM(R9:U9)</f>
+        <v>330</v>
+      </c>
+      <c r="W9" s="15">
+        <v>97</v>
+      </c>
+      <c r="X9" s="15">
+        <v>103</v>
+      </c>
+      <c r="AA9" s="37">
+        <f>SUM(W9:Z9)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B10" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="I10" s="15">
+        <v>0</v>
+      </c>
+      <c r="J10" s="15">
+        <v>0</v>
+      </c>
+      <c r="M10" s="15">
+        <v>-5</v>
+      </c>
+      <c r="N10" s="15">
+        <v>-8</v>
+      </c>
+      <c r="O10" s="15">
+        <v>-6</v>
+      </c>
+      <c r="P10" s="15">
+        <v>-6</v>
+      </c>
+      <c r="Q10" s="37">
+        <f>SUM(M10:P10)</f>
+        <v>-25</v>
+      </c>
+      <c r="R10" s="15">
+        <v>-7</v>
+      </c>
+      <c r="S10" s="15">
+        <v>-7</v>
+      </c>
+      <c r="T10" s="15">
+        <v>-6</v>
+      </c>
+      <c r="U10" s="15">
+        <v>-6</v>
+      </c>
+      <c r="V10" s="37">
+        <f>SUM(R10:U10)</f>
+        <v>-26</v>
+      </c>
+      <c r="W10" s="15">
+        <v>-5</v>
+      </c>
+      <c r="X10" s="15">
+        <v>-7</v>
+      </c>
+      <c r="AA10" s="37">
+        <f>SUM(W10:Z10)</f>
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B11" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="I11" s="15">
+        <v>-11</v>
+      </c>
+      <c r="J11" s="15">
+        <v>5</v>
+      </c>
+      <c r="M11" s="15">
+        <v>-6</v>
+      </c>
+      <c r="N11" s="15">
+        <v>-16</v>
+      </c>
+      <c r="O11" s="15">
+        <v>-11</v>
+      </c>
+      <c r="P11" s="15">
+        <v>-11</v>
+      </c>
+      <c r="Q11" s="37">
+        <f>SUM(M11:P11)</f>
+        <v>-44</v>
+      </c>
+      <c r="R11" s="15">
+        <v>-1</v>
+      </c>
+      <c r="S11" s="15">
+        <v>-37</v>
+      </c>
+      <c r="T11" s="15">
+        <v>-25</v>
+      </c>
+      <c r="U11" s="15">
+        <v>-10</v>
+      </c>
+      <c r="V11" s="37">
+        <f>SUM(R11:U11)</f>
+        <v>-73</v>
+      </c>
+      <c r="W11" s="15">
+        <v>9</v>
+      </c>
+      <c r="X11" s="15">
+        <v>-22</v>
+      </c>
+      <c r="AA11" s="37">
+        <f>SUM(W11:Z11)</f>
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:27" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="16">
+        <f t="shared" ref="C12:W12" si="2">SUM(C8:C11)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="16">
+        <f t="shared" si="2"/>
+        <v>1471</v>
+      </c>
+      <c r="J12" s="16">
+        <f t="shared" si="2"/>
+        <v>1596</v>
+      </c>
+      <c r="K12" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="16">
+        <f t="shared" si="2"/>
+        <v>1643</v>
+      </c>
+      <c r="N12" s="16">
+        <f t="shared" si="2"/>
+        <v>1707</v>
+      </c>
+      <c r="O12" s="16">
+        <f t="shared" si="2"/>
+        <v>1797</v>
+      </c>
+      <c r="P12" s="16">
+        <f t="shared" si="2"/>
+        <v>1916</v>
+      </c>
+      <c r="Q12" s="39">
+        <f t="shared" si="2"/>
+        <v>7063</v>
+      </c>
+      <c r="R12" s="16">
+        <f t="shared" si="2"/>
+        <v>1944</v>
+      </c>
+      <c r="S12" s="16">
+        <f t="shared" si="2"/>
+        <v>1900</v>
+      </c>
+      <c r="T12" s="16">
+        <f t="shared" si="2"/>
+        <v>2056</v>
+      </c>
+      <c r="U12" s="16">
+        <f t="shared" si="2"/>
+        <v>2101</v>
+      </c>
+      <c r="V12" s="39">
+        <f t="shared" si="2"/>
+        <v>8001</v>
+      </c>
+      <c r="W12" s="16">
+        <f t="shared" si="2"/>
+        <v>2104</v>
+      </c>
+      <c r="X12" s="16">
+        <f>SUM(X8:X11)</f>
+        <v>2190</v>
+      </c>
+      <c r="Y12" s="16">
+        <f t="shared" ref="Y12:AA12" si="3">SUM(Y8:Y11)</f>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA12" s="39">
+        <f t="shared" si="3"/>
+        <v>4294</v>
+      </c>
+    </row>
+    <row r="13" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B13" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="I13" s="15">
+        <v>-255</v>
+      </c>
+      <c r="J13" s="15">
+        <v>-240</v>
+      </c>
+      <c r="M13" s="15">
+        <v>-286</v>
+      </c>
+      <c r="N13" s="15">
+        <v>-318</v>
+      </c>
+      <c r="O13" s="15">
+        <v>-240</v>
+      </c>
+      <c r="P13" s="15">
+        <v>-300</v>
+      </c>
+      <c r="Q13" s="37">
+        <f>SUM(M13:P13)</f>
+        <v>-1144</v>
+      </c>
+      <c r="R13" s="15">
+        <v>-273</v>
+      </c>
+      <c r="S13" s="15">
+        <v>-301</v>
+      </c>
+      <c r="T13" s="15">
+        <v>-313</v>
+      </c>
+      <c r="U13" s="15">
+        <v>-337</v>
+      </c>
+      <c r="V13" s="37">
+        <f>SUM(R13:U13)</f>
+        <v>-1224</v>
+      </c>
+      <c r="W13" s="15">
+        <v>-337</v>
+      </c>
+      <c r="X13" s="15">
+        <v>-335</v>
+      </c>
+      <c r="AA13" s="37">
+        <f>SUM(W13:Z13)</f>
+        <v>-672</v>
+      </c>
+    </row>
+    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14" s="15">
+        <v>-9</v>
+      </c>
+      <c r="J14" s="15">
+        <v>-10</v>
+      </c>
+      <c r="M14" s="15">
+        <v>-11</v>
+      </c>
+      <c r="N14" s="15">
+        <v>-13</v>
+      </c>
+      <c r="O14" s="15">
+        <v>-10</v>
+      </c>
+      <c r="P14" s="15">
+        <v>-12</v>
+      </c>
+      <c r="Q14" s="37">
+        <f>SUM(M14:P14)</f>
+        <v>-46</v>
+      </c>
+      <c r="R14" s="15">
+        <v>-13</v>
+      </c>
+      <c r="S14" s="15">
+        <v>-13</v>
+      </c>
+      <c r="T14" s="15">
+        <v>-15</v>
+      </c>
+      <c r="U14" s="15">
+        <v>-16</v>
+      </c>
+      <c r="V14" s="37">
+        <f>SUM(R14:U14)</f>
+        <v>-57</v>
+      </c>
+      <c r="W14" s="15">
+        <v>-18</v>
+      </c>
+      <c r="X14" s="15">
+        <v>-20</v>
+      </c>
+      <c r="AA14" s="37">
+        <f>SUM(W14:Z14)</f>
+        <v>-38</v>
+      </c>
+    </row>
+    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B15" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="15">
+        <v>-138</v>
+      </c>
+      <c r="J15" s="15">
+        <v>-145</v>
+      </c>
+      <c r="M15" s="15">
+        <v>-115</v>
+      </c>
+      <c r="N15" s="15">
+        <v>-105</v>
+      </c>
+      <c r="O15" s="15">
+        <v>-114</v>
+      </c>
+      <c r="P15" s="15">
+        <v>-95</v>
+      </c>
+      <c r="Q15" s="37">
+        <f>SUM(M15:P15)</f>
+        <v>-429</v>
+      </c>
+      <c r="R15" s="15">
+        <v>-97</v>
+      </c>
+      <c r="S15" s="15">
+        <v>-96</v>
+      </c>
+      <c r="T15" s="15">
+        <v>-104</v>
+      </c>
+      <c r="U15" s="15">
+        <v>-92</v>
+      </c>
+      <c r="V15" s="37">
+        <f>SUM(R15:U15)</f>
+        <v>-389</v>
+      </c>
+      <c r="W15" s="15">
+        <v>-96</v>
+      </c>
+      <c r="X15" s="15">
+        <v>-98</v>
+      </c>
+      <c r="AA15" s="37">
+        <f>SUM(W15:Z15)</f>
+        <v>-194</v>
+      </c>
+    </row>
+    <row r="16" spans="2:27" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="16">
+        <f t="shared" ref="C16:W16" si="4">SUM(C12:C15)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="4"/>
+        <v>1069</v>
+      </c>
+      <c r="J16" s="16">
+        <f t="shared" si="4"/>
+        <v>1201</v>
+      </c>
+      <c r="K16" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="4"/>
+        <v>1231</v>
+      </c>
+      <c r="N16" s="16">
+        <f t="shared" si="4"/>
+        <v>1271</v>
+      </c>
+      <c r="O16" s="16">
+        <f t="shared" si="4"/>
+        <v>1433</v>
+      </c>
+      <c r="P16" s="16">
+        <f t="shared" si="4"/>
+        <v>1509</v>
+      </c>
+      <c r="Q16" s="39">
+        <f t="shared" si="4"/>
+        <v>5444</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="4"/>
+        <v>1561</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="4"/>
+        <v>1490</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="4"/>
+        <v>1624</v>
+      </c>
+      <c r="U16" s="16">
+        <f t="shared" si="4"/>
+        <v>1656</v>
+      </c>
+      <c r="V16" s="39">
+        <f t="shared" si="4"/>
+        <v>6331</v>
+      </c>
+      <c r="W16" s="16">
+        <f t="shared" si="4"/>
+        <v>1653</v>
+      </c>
+      <c r="X16" s="16">
+        <f>SUM(X12:X15)</f>
+        <v>1737</v>
+      </c>
+      <c r="Y16" s="16">
+        <f t="shared" ref="Y16:AA16" si="5">SUM(Y12:Y15)</f>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="39">
+        <f t="shared" si="5"/>
+        <v>3390</v>
+      </c>
+    </row>
+    <row r="17" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B17" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="15">
+        <v>-679</v>
+      </c>
+      <c r="J17" s="15">
+        <v>-896</v>
+      </c>
+      <c r="M17" s="15">
+        <v>-915</v>
+      </c>
+      <c r="N17" s="15">
+        <v>-759</v>
+      </c>
+      <c r="O17" s="15">
+        <v>-815</v>
+      </c>
+      <c r="P17" s="15">
+        <v>-985</v>
+      </c>
+      <c r="Q17" s="37">
+        <f>SUM(M17:P17)</f>
+        <v>-3474</v>
+      </c>
+      <c r="R17" s="15">
+        <v>-865</v>
+      </c>
+      <c r="S17" s="15">
+        <v>-728</v>
+      </c>
+      <c r="T17" s="15">
+        <v>-744</v>
+      </c>
+      <c r="U17" s="15">
+        <v>-763</v>
+      </c>
+      <c r="V17" s="37">
+        <f>SUM(R17:U17)</f>
+        <v>-3100</v>
+      </c>
+      <c r="W17" s="15">
+        <v>-748</v>
+      </c>
+      <c r="X17" s="15">
+        <v>-703</v>
+      </c>
+      <c r="AA17" s="37">
+        <f>SUM(W17:Z17)</f>
+        <v>-1451</v>
+      </c>
+    </row>
+    <row r="18" spans="2:27" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="C18" s="16">
+        <f t="shared" ref="C18:W18" si="6">SUM(C16:C17)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="16">
+        <f t="shared" si="6"/>
+        <v>390</v>
+      </c>
+      <c r="J18" s="16">
+        <f t="shared" si="6"/>
+        <v>305</v>
+      </c>
+      <c r="K18" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="16">
+        <f t="shared" si="6"/>
+        <v>316</v>
+      </c>
+      <c r="N18" s="16">
+        <f t="shared" si="6"/>
+        <v>512</v>
+      </c>
+      <c r="O18" s="16">
+        <f t="shared" si="6"/>
+        <v>618</v>
+      </c>
+      <c r="P18" s="16">
+        <f t="shared" si="6"/>
+        <v>524</v>
+      </c>
+      <c r="Q18" s="39">
+        <f t="shared" si="6"/>
+        <v>1970</v>
+      </c>
+      <c r="R18" s="16">
+        <f t="shared" si="6"/>
+        <v>696</v>
+      </c>
+      <c r="S18" s="16">
+        <f t="shared" si="6"/>
+        <v>762</v>
+      </c>
+      <c r="T18" s="16">
+        <f t="shared" si="6"/>
+        <v>880</v>
+      </c>
+      <c r="U18" s="16">
+        <f t="shared" si="6"/>
+        <v>893</v>
+      </c>
+      <c r="V18" s="39">
+        <f t="shared" si="6"/>
+        <v>3231</v>
+      </c>
+      <c r="W18" s="16">
+        <f t="shared" si="6"/>
+        <v>905</v>
+      </c>
+      <c r="X18" s="16">
+        <f>SUM(X16:X17)</f>
+        <v>1034</v>
+      </c>
+      <c r="Y18" s="16">
+        <f t="shared" ref="Y18:AA18" si="7">SUM(Y16:Y17)</f>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="39">
+        <f t="shared" si="7"/>
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="19" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B19" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="P19" s="15">
+        <v>-101</v>
+      </c>
+      <c r="Q19" s="37"/>
+      <c r="R19" s="15">
+        <v>-151</v>
+      </c>
+      <c r="S19" s="15">
+        <v>-168</v>
+      </c>
+      <c r="T19" s="15">
+        <v>-195</v>
+      </c>
+      <c r="U19" s="15">
+        <v>-187</v>
+      </c>
+      <c r="V19" s="37">
+        <f>SUM(R19:U19)</f>
+        <v>-701</v>
+      </c>
+      <c r="W19" s="15">
+        <v>-223</v>
+      </c>
+      <c r="X19" s="15">
+        <v>-235</v>
+      </c>
+      <c r="AA19" s="37">
+        <f>SUM(W19:Z19)</f>
+        <v>-458</v>
+      </c>
+    </row>
+    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B20" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="P20" s="15">
+        <v>-41</v>
+      </c>
+      <c r="Q20" s="37"/>
+      <c r="R20" s="15">
+        <v>-37</v>
+      </c>
+      <c r="S20" s="15">
+        <v>-37</v>
+      </c>
+      <c r="T20" s="15">
+        <v>-37</v>
+      </c>
+      <c r="U20" s="15">
+        <v>-41</v>
+      </c>
+      <c r="V20" s="37">
+        <f>SUM(R20:U20)</f>
+        <v>-152</v>
+      </c>
+      <c r="W20" s="15">
+        <v>-44</v>
+      </c>
+      <c r="X20" s="15">
+        <v>-46</v>
+      </c>
+      <c r="AA20" s="37">
+        <f>SUM(W20:Z20)</f>
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="21" spans="2:27" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="16">
+        <f t="shared" ref="R21:W21" si="8">SUM(R18:R20)</f>
+        <v>508</v>
+      </c>
+      <c r="S21" s="16">
+        <f t="shared" si="8"/>
+        <v>557</v>
+      </c>
+      <c r="T21" s="16">
+        <f t="shared" si="8"/>
+        <v>648</v>
+      </c>
+      <c r="U21" s="16">
+        <f t="shared" si="8"/>
+        <v>665</v>
+      </c>
+      <c r="V21" s="39">
+        <f t="shared" si="8"/>
+        <v>2378</v>
+      </c>
+      <c r="W21" s="16">
+        <f t="shared" si="8"/>
+        <v>638</v>
+      </c>
+      <c r="X21" s="16">
+        <f>SUM(X18:X20)</f>
+        <v>753</v>
+      </c>
+      <c r="Y21" s="16">
+        <f t="shared" ref="Y21:AA21" si="9">SUM(Y18:Y20)</f>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="39">
+        <f t="shared" si="9"/>
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="22" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B22" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q22" s="37"/>
+      <c r="R22" s="15">
+        <v>500</v>
+      </c>
+      <c r="S22" s="15">
+        <v>500</v>
+      </c>
+      <c r="T22" s="15">
+        <v>500</v>
+      </c>
+      <c r="U22" s="15">
+        <v>500</v>
+      </c>
+      <c r="V22" s="37">
+        <v>500</v>
+      </c>
+      <c r="W22" s="15">
+        <v>500</v>
+      </c>
+      <c r="X22" s="15">
+        <v>500</v>
+      </c>
+      <c r="Y22" s="15">
+        <v>500</v>
+      </c>
+      <c r="Z22" s="15">
+        <v>500</v>
+      </c>
+      <c r="AA22" s="37">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="23" spans="2:27" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="93"/>
+      <c r="R23" s="31">
+        <f t="shared" ref="R23:W23" si="10">R21/R22</f>
+        <v>1.016</v>
+      </c>
+      <c r="S23" s="31">
+        <f t="shared" si="10"/>
+        <v>1.1140000000000001</v>
+      </c>
+      <c r="T23" s="31">
+        <f t="shared" si="10"/>
+        <v>1.296</v>
+      </c>
+      <c r="U23" s="31">
+        <f t="shared" si="10"/>
+        <v>1.33</v>
+      </c>
+      <c r="V23" s="93">
+        <f t="shared" si="10"/>
+        <v>4.7560000000000002</v>
+      </c>
+      <c r="W23" s="31">
+        <f t="shared" si="10"/>
+        <v>1.276</v>
+      </c>
+      <c r="X23" s="31">
+        <f>X21/X22</f>
+        <v>1.506</v>
+      </c>
+      <c r="Y23" s="31">
+        <f t="shared" ref="Y23:AA23" si="11">Y21/Y22</f>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="31">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AA23" s="93">
+        <f t="shared" si="11"/>
+        <v>2.782</v>
+      </c>
+    </row>
+    <row r="24" spans="2:27" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q24" s="39"/>
+      <c r="V24" s="39"/>
+      <c r="AA24" s="39"/>
+    </row>
+    <row r="25" spans="2:27" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="51" t="s">
+        <v>236</v>
+      </c>
+      <c r="J25" s="51">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="O25" s="51">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="P25" s="51">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="Q25" s="92"/>
+      <c r="R25" s="51">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="S25" s="51">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="T25" s="51">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="U25" s="51">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="V25" s="92"/>
+      <c r="W25" s="51">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="X25" s="51">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="AA25" s="92"/>
+    </row>
+    <row r="26" spans="2:27" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="J26" s="51">
+        <v>0.247</v>
+      </c>
+      <c r="O26" s="51">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="P26" s="51">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="Q26" s="92"/>
+      <c r="R26" s="51">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="S26" s="51">
+        <v>0.216</v>
+      </c>
+      <c r="T26" s="51">
+        <v>0.21</v>
+      </c>
+      <c r="U26" s="51">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="V26" s="92"/>
+      <c r="W26" s="51">
+        <v>0.214</v>
+      </c>
+      <c r="X26" s="51">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="AA26" s="92"/>
+    </row>
+    <row r="27" spans="2:27" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="51" t="s">
+        <v>238</v>
+      </c>
+      <c r="J27" s="51">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="O27" s="51">
+        <v>3.9E-2</v>
+      </c>
+      <c r="P27" s="51">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="Q27" s="92"/>
+      <c r="R27" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="S27" s="51">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="T27" s="51">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="U27" s="51">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="V27" s="92"/>
+      <c r="W27" s="51">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="X27" s="51">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA27" s="92"/>
+    </row>
+    <row r="28" spans="2:27" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="J28" s="51">
+        <v>0.12</v>
+      </c>
+      <c r="O28" s="51">
+        <v>0.188</v>
+      </c>
+      <c r="P28" s="51">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="Q28" s="92"/>
+      <c r="R28" s="51">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="S28" s="51">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="T28" s="51">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="U28" s="51">
+        <v>0.224</v>
+      </c>
+      <c r="V28" s="92"/>
+      <c r="W28" s="51">
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="X28" s="51">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="AA28" s="92"/>
+    </row>
+    <row r="29" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="Q29" s="37"/>
+      <c r="V29" s="37"/>
+      <c r="AA29" s="37"/>
+    </row>
+    <row r="30" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B30" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q30" s="37"/>
+      <c r="V30" s="37"/>
+      <c r="AA30" s="37"/>
+    </row>
+    <row r="31" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B31" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I31" s="15">
+        <v>398</v>
+      </c>
+      <c r="J31" s="15">
+        <v>445</v>
+      </c>
+      <c r="M31" s="15">
+        <v>511</v>
+      </c>
+      <c r="N31" s="15">
+        <v>536</v>
+      </c>
+      <c r="O31" s="15">
+        <v>574</v>
+      </c>
+      <c r="P31" s="15">
+        <v>626</v>
+      </c>
+      <c r="Q31" s="37">
+        <f>SUM(M31:P31)</f>
+        <v>2247</v>
+      </c>
+      <c r="R31" s="15">
+        <v>632</v>
+      </c>
+      <c r="S31" s="15">
+        <v>634</v>
+      </c>
+      <c r="T31" s="15">
+        <v>652</v>
+      </c>
+      <c r="U31" s="15">
+        <v>680</v>
+      </c>
+      <c r="V31" s="37">
+        <f>SUM(R31:U31)</f>
+        <v>2598</v>
+      </c>
+      <c r="W31" s="15">
+        <v>669</v>
+      </c>
+      <c r="X31" s="15">
+        <v>700</v>
+      </c>
+      <c r="AA31" s="37">
+        <f>SUM(W31:Z31)</f>
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B32" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="I32" s="15">
+        <v>-71</v>
+      </c>
+      <c r="J32" s="15">
+        <v>-97</v>
+      </c>
+      <c r="M32" s="15">
+        <v>-134</v>
+      </c>
+      <c r="N32" s="15">
+        <v>-140</v>
+      </c>
+      <c r="O32" s="15">
+        <v>-145</v>
+      </c>
+      <c r="P32" s="15">
+        <v>-145</v>
+      </c>
+      <c r="Q32" s="37">
+        <f>SUM(M32:P32)</f>
+        <v>-564</v>
+      </c>
+      <c r="R32" s="15">
+        <v>-159</v>
+      </c>
+      <c r="S32" s="15">
+        <v>-151</v>
+      </c>
+      <c r="T32" s="15">
+        <v>-148</v>
+      </c>
+      <c r="U32" s="15">
+        <v>-145</v>
+      </c>
+      <c r="V32" s="37">
+        <f>SUM(R32:U32)</f>
+        <v>-603</v>
+      </c>
+      <c r="W32" s="15">
+        <v>-144</v>
+      </c>
+      <c r="X32" s="15">
+        <v>-157</v>
+      </c>
+      <c r="AA32" s="37">
+        <f>SUM(W32:Z32)</f>
+        <v>-301</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B33" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="16">
+        <f t="shared" ref="C33" si="12">SUM(C31:C32)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="16">
+        <f t="shared" ref="D33" si="13">SUM(D31:D32)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="16">
+        <f t="shared" ref="E33" si="14">SUM(E31:E32)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="16">
+        <f t="shared" ref="F33" si="15">SUM(F31:F32)</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="16">
+        <f t="shared" ref="G33" si="16">SUM(G31:G32)</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="16">
+        <f t="shared" ref="H33" si="17">SUM(H31:H32)</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="16">
+        <f t="shared" ref="I33" si="18">SUM(I31:I32)</f>
+        <v>327</v>
+      </c>
+      <c r="J33" s="16">
+        <f t="shared" ref="J33" si="19">SUM(J31:J32)</f>
+        <v>348</v>
+      </c>
+      <c r="K33" s="16">
+        <f t="shared" ref="K33" si="20">SUM(K31:K32)</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="16">
+        <f t="shared" ref="L33" si="21">SUM(L31:L32)</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="16">
+        <f t="shared" ref="M33" si="22">SUM(M31:M32)</f>
+        <v>377</v>
+      </c>
+      <c r="N33" s="16">
+        <f t="shared" ref="N33" si="23">SUM(N31:N32)</f>
+        <v>396</v>
+      </c>
+      <c r="O33" s="16">
+        <f t="shared" ref="O33" si="24">SUM(O31:O32)</f>
+        <v>429</v>
+      </c>
+      <c r="P33" s="16">
+        <f t="shared" ref="P33:Q33" si="25">SUM(P31:P32)</f>
+        <v>481</v>
+      </c>
+      <c r="Q33" s="39">
+        <f t="shared" si="25"/>
+        <v>1683</v>
+      </c>
+      <c r="R33" s="16">
+        <f t="shared" ref="R33" si="26">SUM(R31:R32)</f>
+        <v>473</v>
+      </c>
+      <c r="S33" s="16">
+        <f t="shared" ref="S33" si="27">SUM(S31:S32)</f>
+        <v>483</v>
+      </c>
+      <c r="T33" s="16">
+        <f t="shared" ref="T33" si="28">SUM(T31:T32)</f>
+        <v>504</v>
+      </c>
+      <c r="U33" s="16">
+        <f t="shared" ref="U33:V33" si="29">SUM(U31:U32)</f>
+        <v>535</v>
+      </c>
+      <c r="V33" s="39">
+        <f t="shared" si="29"/>
+        <v>1995</v>
+      </c>
+      <c r="W33" s="16">
+        <f t="shared" ref="W33" si="30">SUM(W31:W32)</f>
+        <v>525</v>
+      </c>
+      <c r="X33" s="16">
+        <f>SUM(X31:X32)</f>
+        <v>543</v>
+      </c>
+      <c r="Y33" s="16">
+        <f t="shared" ref="Y33:AA33" si="31">SUM(Y31:Y32)</f>
+        <v>0</v>
+      </c>
+      <c r="Z33" s="16">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AA33" s="39">
+        <f t="shared" si="31"/>
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B34" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I34" s="15">
+        <v>141</v>
+      </c>
+      <c r="J34" s="15">
+        <v>141</v>
+      </c>
+      <c r="M34" s="15">
+        <v>139</v>
+      </c>
+      <c r="N34" s="15">
+        <v>175</v>
+      </c>
+      <c r="O34" s="15">
+        <v>173</v>
+      </c>
+      <c r="P34" s="15">
+        <v>169</v>
+      </c>
+      <c r="Q34" s="37">
+        <f>SUM(M34:P34)</f>
+        <v>656</v>
+      </c>
+      <c r="R34" s="15">
+        <v>195</v>
+      </c>
+      <c r="S34" s="15">
+        <v>214</v>
+      </c>
+      <c r="T34" s="15">
+        <v>230</v>
+      </c>
+      <c r="U34" s="15">
+        <v>184</v>
+      </c>
+      <c r="V34" s="37">
+        <f>SUM(R34:U34)</f>
+        <v>823</v>
+      </c>
+      <c r="W34" s="15">
+        <v>198</v>
+      </c>
+      <c r="X34" s="15">
+        <v>213</v>
+      </c>
+      <c r="AA34" s="37">
+        <f>SUM(W34:Z34)</f>
+        <v>411</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B35" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="I35" s="15">
+        <v>-46</v>
+      </c>
+      <c r="J35" s="15">
+        <v>-58</v>
+      </c>
+      <c r="M35" s="15">
+        <v>-61</v>
+      </c>
+      <c r="N35" s="15">
+        <v>-69</v>
+      </c>
+      <c r="O35" s="15">
+        <v>-63</v>
+      </c>
+      <c r="P35" s="15">
+        <v>-70</v>
+      </c>
+      <c r="Q35" s="37">
+        <f>SUM(M35:P35)</f>
+        <v>-263</v>
+      </c>
+      <c r="R35" s="15">
+        <v>-66</v>
+      </c>
+      <c r="S35" s="15">
+        <v>-79</v>
+      </c>
+      <c r="T35" s="15">
+        <v>-67</v>
+      </c>
+      <c r="U35" s="15">
+        <v>-80</v>
+      </c>
+      <c r="V35" s="37">
+        <f>SUM(R35:U35)</f>
+        <v>-292</v>
+      </c>
+      <c r="W35" s="15">
+        <v>-84</v>
+      </c>
+      <c r="X35" s="15">
+        <v>-91</v>
+      </c>
+      <c r="AA35" s="37">
+        <f>SUM(W35:Z35)</f>
+        <v>-175</v>
+      </c>
+    </row>
+    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B36" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="I36" s="15">
+        <v>-2</v>
+      </c>
+      <c r="J36" s="15">
+        <v>1</v>
+      </c>
+      <c r="M36" s="15">
+        <v>-1</v>
+      </c>
+      <c r="N36" s="15">
+        <v>-1</v>
+      </c>
+      <c r="O36" s="15">
+        <v>-2</v>
+      </c>
+      <c r="P36" s="15">
+        <v>-3</v>
+      </c>
+      <c r="Q36" s="37">
+        <f>SUM(M36:P36)</f>
+        <v>-7</v>
+      </c>
+      <c r="R36" s="15">
+        <v>0</v>
+      </c>
+      <c r="S36" s="15">
+        <v>-8</v>
+      </c>
+      <c r="T36" s="15">
+        <v>-5</v>
+      </c>
+      <c r="U36" s="15">
+        <v>-3</v>
+      </c>
+      <c r="V36" s="37">
+        <f>SUM(R36:U36)</f>
+        <v>-16</v>
+      </c>
+      <c r="W36" s="15">
+        <v>2</v>
+      </c>
+      <c r="X36" s="15">
+        <v>-5</v>
+      </c>
+      <c r="AA36" s="37">
+        <f>SUM(W36:Z36)</f>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B37" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="16">
+        <f t="shared" ref="C37" si="32">SUM(C33:C36)</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="16">
+        <f t="shared" ref="D37" si="33">SUM(D33:D36)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="16">
+        <f t="shared" ref="E37" si="34">SUM(E33:E36)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="16">
+        <f t="shared" ref="F37" si="35">SUM(F33:F36)</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="16">
+        <f t="shared" ref="G37" si="36">SUM(G33:G36)</f>
+        <v>0</v>
+      </c>
+      <c r="H37" s="16">
+        <f t="shared" ref="H37" si="37">SUM(H33:H36)</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="16">
+        <f t="shared" ref="I37" si="38">SUM(I33:I36)</f>
+        <v>420</v>
+      </c>
+      <c r="J37" s="16">
+        <f t="shared" ref="J37" si="39">SUM(J33:J36)</f>
+        <v>432</v>
+      </c>
+      <c r="K37" s="16">
+        <f t="shared" ref="K37" si="40">SUM(K33:K36)</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="16">
+        <f t="shared" ref="L37" si="41">SUM(L33:L36)</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="16">
+        <f t="shared" ref="M37" si="42">SUM(M33:M36)</f>
+        <v>454</v>
+      </c>
+      <c r="N37" s="16">
+        <f t="shared" ref="N37" si="43">SUM(N33:N36)</f>
+        <v>501</v>
+      </c>
+      <c r="O37" s="16">
+        <f t="shared" ref="O37" si="44">SUM(O33:O36)</f>
+        <v>537</v>
+      </c>
+      <c r="P37" s="16">
+        <f t="shared" ref="P37:Q37" si="45">SUM(P33:P36)</f>
+        <v>577</v>
+      </c>
+      <c r="Q37" s="39">
+        <f t="shared" si="45"/>
+        <v>2069</v>
+      </c>
+      <c r="R37" s="16">
+        <f t="shared" ref="R37" si="46">SUM(R33:R36)</f>
+        <v>602</v>
+      </c>
+      <c r="S37" s="16">
+        <f t="shared" ref="S37" si="47">SUM(S33:S36)</f>
+        <v>610</v>
+      </c>
+      <c r="T37" s="16">
+        <f t="shared" ref="T37" si="48">SUM(T33:T36)</f>
+        <v>662</v>
+      </c>
+      <c r="U37" s="16">
+        <f t="shared" ref="U37:V37" si="49">SUM(U33:U36)</f>
+        <v>636</v>
+      </c>
+      <c r="V37" s="39">
+        <f t="shared" si="49"/>
+        <v>2510</v>
+      </c>
+      <c r="W37" s="16">
+        <f t="shared" ref="W37" si="50">SUM(W33:W36)</f>
+        <v>641</v>
+      </c>
+      <c r="X37" s="16">
+        <f>SUM(X33:X36)</f>
+        <v>660</v>
+      </c>
+      <c r="Y37" s="16">
+        <f t="shared" ref="Y37:AA37" si="51">SUM(Y33:Y36)</f>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="16">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="AA37" s="39">
+        <f t="shared" si="51"/>
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B38" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="I38" s="15">
+        <v>-57</v>
+      </c>
+      <c r="J38" s="15">
+        <v>-53</v>
+      </c>
+      <c r="M38" s="15">
+        <v>-64</v>
+      </c>
+      <c r="N38" s="15">
+        <v>-61</v>
+      </c>
+      <c r="O38" s="15">
+        <v>-61</v>
+      </c>
+      <c r="P38" s="15">
+        <v>-75</v>
+      </c>
+      <c r="Q38" s="37">
+        <f>SUM(M38:P38)</f>
+        <v>-261</v>
+      </c>
+      <c r="R38" s="15">
+        <v>-67</v>
+      </c>
+      <c r="S38" s="15">
+        <v>-57</v>
+      </c>
+      <c r="T38" s="15">
+        <v>-54</v>
+      </c>
+      <c r="U38" s="15">
+        <v>-63</v>
+      </c>
+      <c r="V38" s="37">
+        <f>SUM(R38:U38)</f>
+        <v>-241</v>
+      </c>
+      <c r="W38" s="15">
+        <v>-61</v>
+      </c>
+      <c r="X38" s="15">
+        <v>-67</v>
+      </c>
+      <c r="AA38" s="37">
+        <f>SUM(W38:Z38)</f>
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B39" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I39" s="15">
+        <v>-22</v>
+      </c>
+      <c r="J39" s="15">
+        <v>-4</v>
+      </c>
+      <c r="M39" s="15">
+        <v>-3</v>
+      </c>
+      <c r="N39" s="15">
+        <v>-2</v>
+      </c>
+      <c r="O39" s="15">
+        <v>-6</v>
+      </c>
+      <c r="P39" s="15">
+        <v>-4</v>
+      </c>
+      <c r="Q39" s="37">
+        <f>SUM(M39:P39)</f>
+        <v>-15</v>
+      </c>
+      <c r="R39" s="15">
+        <v>-5</v>
+      </c>
+      <c r="S39" s="15">
+        <v>-4</v>
+      </c>
+      <c r="T39" s="15">
+        <v>-5</v>
+      </c>
+      <c r="U39" s="15">
+        <v>-5</v>
+      </c>
+      <c r="V39" s="37">
+        <f>SUM(R39:U39)</f>
+        <v>-19</v>
+      </c>
+      <c r="W39" s="15">
+        <v>-5</v>
+      </c>
+      <c r="X39" s="15">
+        <v>-6</v>
+      </c>
+      <c r="AA39" s="37">
+        <f>SUM(W39:Z39)</f>
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B40" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="I40" s="15">
+        <v>-127</v>
+      </c>
+      <c r="J40" s="15">
+        <v>-155</v>
+      </c>
+      <c r="M40" s="15">
+        <v>-81</v>
+      </c>
+      <c r="N40" s="15">
+        <v>-110</v>
+      </c>
+      <c r="O40" s="15">
+        <v>-112</v>
+      </c>
+      <c r="P40" s="15">
+        <v>-97</v>
+      </c>
+      <c r="Q40" s="37">
+        <f>SUM(M40:P40)</f>
+        <v>-400</v>
+      </c>
+      <c r="R40" s="15">
+        <v>-97</v>
+      </c>
+      <c r="S40" s="15">
+        <v>-70</v>
+      </c>
+      <c r="T40" s="15">
+        <v>-111</v>
+      </c>
+      <c r="U40" s="15">
+        <v>-110</v>
+      </c>
+      <c r="V40" s="37">
+        <f>SUM(R40:U40)</f>
+        <v>-388</v>
+      </c>
+      <c r="W40" s="15">
+        <v>-86</v>
+      </c>
+      <c r="X40" s="15">
+        <v>-106</v>
+      </c>
+      <c r="AA40" s="37">
+        <f>SUM(W40:Z40)</f>
+        <v>-192</v>
+      </c>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="16">
+        <f t="shared" ref="C41" si="52">SUM(C37:C40)</f>
+        <v>0</v>
+      </c>
+      <c r="D41" s="16">
+        <f t="shared" ref="D41" si="53">SUM(D37:D40)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="16">
+        <f t="shared" ref="E41" si="54">SUM(E37:E40)</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="16">
+        <f t="shared" ref="F41" si="55">SUM(F37:F40)</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="16">
+        <f t="shared" ref="G41" si="56">SUM(G37:G40)</f>
+        <v>0</v>
+      </c>
+      <c r="H41" s="16">
+        <f t="shared" ref="H41" si="57">SUM(H37:H40)</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="16">
+        <f t="shared" ref="I41" si="58">SUM(I37:I40)</f>
+        <v>214</v>
+      </c>
+      <c r="J41" s="16">
+        <f t="shared" ref="J41" si="59">SUM(J37:J40)</f>
+        <v>220</v>
+      </c>
+      <c r="K41" s="16">
+        <f t="shared" ref="K41" si="60">SUM(K37:K40)</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="16">
+        <f t="shared" ref="L41" si="61">SUM(L37:L40)</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="16">
+        <f t="shared" ref="M41" si="62">SUM(M37:M40)</f>
+        <v>306</v>
+      </c>
+      <c r="N41" s="16">
+        <f t="shared" ref="N41" si="63">SUM(N37:N40)</f>
+        <v>328</v>
+      </c>
+      <c r="O41" s="16">
+        <f t="shared" ref="O41" si="64">SUM(O37:O40)</f>
+        <v>358</v>
+      </c>
+      <c r="P41" s="16">
+        <f t="shared" ref="P41:Q41" si="65">SUM(P37:P40)</f>
+        <v>401</v>
+      </c>
+      <c r="Q41" s="39">
+        <f t="shared" si="65"/>
+        <v>1393</v>
+      </c>
+      <c r="R41" s="16">
+        <f t="shared" ref="R41" si="66">SUM(R37:R40)</f>
+        <v>433</v>
+      </c>
+      <c r="S41" s="16">
+        <f t="shared" ref="S41" si="67">SUM(S37:S40)</f>
+        <v>479</v>
+      </c>
+      <c r="T41" s="16">
+        <f t="shared" ref="T41" si="68">SUM(T37:T40)</f>
+        <v>492</v>
+      </c>
+      <c r="U41" s="16">
+        <f t="shared" ref="U41:V41" si="69">SUM(U37:U40)</f>
+        <v>458</v>
+      </c>
+      <c r="V41" s="39">
+        <f t="shared" si="69"/>
+        <v>1862</v>
+      </c>
+      <c r="W41" s="16">
+        <f t="shared" ref="W41" si="70">SUM(W37:W40)</f>
+        <v>489</v>
+      </c>
+      <c r="X41" s="16">
+        <f>SUM(X37:X40)</f>
+        <v>481</v>
+      </c>
+      <c r="Y41" s="16">
+        <f t="shared" ref="Y41:AA41" si="71">SUM(Y37:Y40)</f>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="16">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="AA41" s="39">
+        <f t="shared" si="71"/>
+        <v>970</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B42" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I42" s="15">
+        <v>-90</v>
+      </c>
+      <c r="J42" s="15">
+        <v>-135</v>
+      </c>
+      <c r="M42" s="15">
+        <v>-137</v>
+      </c>
+      <c r="N42" s="15">
+        <v>-128</v>
+      </c>
+      <c r="O42" s="15">
+        <v>-131</v>
+      </c>
+      <c r="P42" s="15">
+        <v>-130</v>
+      </c>
+      <c r="Q42" s="37">
+        <f>SUM(M42:P42)</f>
+        <v>-526</v>
+      </c>
+      <c r="R42" s="15">
+        <v>-133</v>
+      </c>
+      <c r="S42" s="15">
+        <v>-137</v>
+      </c>
+      <c r="T42" s="15">
+        <v>-140</v>
+      </c>
+      <c r="U42" s="15">
+        <v>-185</v>
+      </c>
+      <c r="V42" s="37">
+        <f>SUM(R42:U42)</f>
+        <v>-595</v>
+      </c>
+      <c r="W42" s="15">
+        <v>-155</v>
+      </c>
+      <c r="X42" s="15">
+        <v>-155</v>
+      </c>
+      <c r="AA42" s="37">
+        <f>SUM(W42:Z42)</f>
+        <v>-310</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B43" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="C43" s="16">
+        <f t="shared" ref="C43" si="72">SUM(C41:C42)</f>
+        <v>0</v>
+      </c>
+      <c r="D43" s="16">
+        <f t="shared" ref="D43" si="73">SUM(D41:D42)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="16">
+        <f t="shared" ref="E43" si="74">SUM(E41:E42)</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="16">
+        <f t="shared" ref="F43" si="75">SUM(F41:F42)</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="16">
+        <f t="shared" ref="G43" si="76">SUM(G41:G42)</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="16">
+        <f t="shared" ref="H43" si="77">SUM(H41:H42)</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="16">
+        <f t="shared" ref="I43" si="78">SUM(I41:I42)</f>
+        <v>124</v>
+      </c>
+      <c r="J43" s="16">
+        <f t="shared" ref="J43" si="79">SUM(J41:J42)</f>
+        <v>85</v>
+      </c>
+      <c r="K43" s="16">
+        <f t="shared" ref="K43" si="80">SUM(K41:K42)</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="16">
+        <f t="shared" ref="L43" si="81">SUM(L41:L42)</f>
+        <v>0</v>
+      </c>
+      <c r="M43" s="16">
+        <f t="shared" ref="M43" si="82">SUM(M41:M42)</f>
+        <v>169</v>
+      </c>
+      <c r="N43" s="16">
+        <f t="shared" ref="N43" si="83">SUM(N41:N42)</f>
+        <v>200</v>
+      </c>
+      <c r="O43" s="16">
+        <f t="shared" ref="O43" si="84">SUM(O41:O42)</f>
+        <v>227</v>
+      </c>
+      <c r="P43" s="16">
+        <f t="shared" ref="P43:Q43" si="85">SUM(P41:P42)</f>
+        <v>271</v>
+      </c>
+      <c r="Q43" s="39">
+        <f t="shared" si="85"/>
+        <v>867</v>
+      </c>
+      <c r="R43" s="16">
+        <f t="shared" ref="R43" si="86">SUM(R41:R42)</f>
+        <v>300</v>
+      </c>
+      <c r="S43" s="16">
+        <f t="shared" ref="S43" si="87">SUM(S41:S42)</f>
+        <v>342</v>
+      </c>
+      <c r="T43" s="16">
+        <f t="shared" ref="T43" si="88">SUM(T41:T42)</f>
+        <v>352</v>
+      </c>
+      <c r="U43" s="16">
+        <f t="shared" ref="U43:V43" si="89">SUM(U41:U42)</f>
+        <v>273</v>
+      </c>
+      <c r="V43" s="39">
+        <f t="shared" si="89"/>
+        <v>1267</v>
+      </c>
+      <c r="W43" s="16">
+        <f t="shared" ref="W43" si="90">SUM(W41:W42)</f>
+        <v>334</v>
+      </c>
+      <c r="X43" s="16">
+        <f>SUM(X41:X42)</f>
+        <v>326</v>
+      </c>
+      <c r="Y43" s="16">
+        <f t="shared" ref="Y43:AA43" si="91">SUM(Y41:Y42)</f>
+        <v>0</v>
+      </c>
+      <c r="Z43" s="16">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="AA43" s="39">
+        <f t="shared" si="91"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B44" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="P44" s="15">
+        <v>-52</v>
+      </c>
+      <c r="Q44" s="37"/>
+      <c r="R44" s="15">
+        <v>-65</v>
+      </c>
+      <c r="S44" s="15">
+        <v>-75</v>
+      </c>
+      <c r="T44" s="15">
+        <v>-78</v>
+      </c>
+      <c r="U44" s="15">
+        <v>-57</v>
+      </c>
+      <c r="V44" s="37">
+        <f>SUM(R44:U44)</f>
+        <v>-275</v>
+      </c>
+      <c r="W44" s="15">
+        <v>-83</v>
+      </c>
+      <c r="X44" s="15">
+        <v>-74</v>
+      </c>
+      <c r="AA44" s="37">
+        <f>SUM(W44:Z44)</f>
+        <v>-157</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B45" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="P45" s="15">
+        <v>-8</v>
+      </c>
+      <c r="Q45" s="37"/>
+      <c r="R45" s="15">
+        <v>-8</v>
+      </c>
+      <c r="S45" s="15">
+        <v>-8</v>
+      </c>
+      <c r="T45" s="15">
+        <v>-8</v>
+      </c>
+      <c r="U45" s="15">
+        <v>-9</v>
+      </c>
+      <c r="V45" s="37">
+        <f>SUM(R45:U45)</f>
+        <v>-33</v>
+      </c>
+      <c r="W45" s="15">
+        <v>-9</v>
+      </c>
+      <c r="X45" s="15">
+        <v>-9</v>
+      </c>
+      <c r="AA45" s="37">
+        <f>SUM(W45:Z45)</f>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B46" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16"/>
+      <c r="O46" s="16"/>
+      <c r="P46" s="16"/>
+      <c r="Q46" s="39"/>
+      <c r="R46" s="16">
+        <f t="shared" ref="R46" si="92">SUM(R43:R45)</f>
+        <v>227</v>
+      </c>
+      <c r="S46" s="16">
+        <f t="shared" ref="S46" si="93">SUM(S43:S45)</f>
+        <v>259</v>
+      </c>
+      <c r="T46" s="16">
+        <f t="shared" ref="T46" si="94">SUM(T43:T45)</f>
+        <v>266</v>
+      </c>
+      <c r="U46" s="16">
+        <f t="shared" ref="U46:V46" si="95">SUM(U43:U45)</f>
+        <v>207</v>
+      </c>
+      <c r="V46" s="39">
+        <f t="shared" si="95"/>
+        <v>959</v>
+      </c>
+      <c r="W46" s="16">
+        <f t="shared" ref="W46" si="96">SUM(W43:W45)</f>
+        <v>242</v>
+      </c>
+      <c r="X46" s="16">
+        <f>SUM(X43:X45)</f>
+        <v>243</v>
+      </c>
+      <c r="Y46" s="16">
+        <f t="shared" ref="Y46:AA46" si="97">SUM(Y43:Y45)</f>
+        <v>0</v>
+      </c>
+      <c r="Z46" s="16">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="AA46" s="39">
+        <f t="shared" si="97"/>
+        <v>485</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B47" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q47" s="37"/>
+      <c r="R47" s="15">
+        <v>500</v>
+      </c>
+      <c r="S47" s="15">
+        <v>500</v>
+      </c>
+      <c r="T47" s="15">
+        <v>500</v>
+      </c>
+      <c r="U47" s="15">
+        <v>500</v>
+      </c>
+      <c r="V47" s="37">
+        <v>500</v>
+      </c>
+      <c r="W47" s="15">
+        <v>500</v>
+      </c>
+      <c r="X47" s="15">
+        <v>500</v>
+      </c>
+      <c r="Y47" s="15">
+        <v>500</v>
+      </c>
+      <c r="Z47" s="15">
+        <v>500</v>
+      </c>
+      <c r="AA47" s="37">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="31"/>
+      <c r="I48" s="31"/>
+      <c r="J48" s="31"/>
+      <c r="K48" s="31"/>
+      <c r="L48" s="31"/>
+      <c r="M48" s="31"/>
+      <c r="N48" s="31"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="31"/>
+      <c r="Q48" s="93"/>
+      <c r="R48" s="31">
+        <f t="shared" ref="R48:W48" si="98">R46/R47</f>
+        <v>0.45400000000000001</v>
+      </c>
+      <c r="S48" s="31">
+        <f t="shared" si="98"/>
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="T48" s="31">
+        <f t="shared" si="98"/>
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="U48" s="31">
+        <f t="shared" si="98"/>
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="V48" s="93">
+        <f t="shared" si="98"/>
+        <v>1.9179999999999999</v>
+      </c>
+      <c r="W48" s="31">
+        <f t="shared" si="98"/>
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="X48" s="31">
+        <f>X46/X47</f>
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="Y48" s="31">
+        <f t="shared" ref="Y48:AA48" si="99">Y46/Y47</f>
+        <v>0</v>
+      </c>
+      <c r="Z48" s="31">
+        <f t="shared" si="99"/>
+        <v>0</v>
+      </c>
+      <c r="AA48" s="93">
+        <f t="shared" si="99"/>
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="49" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
+      <c r="N49" s="16"/>
+      <c r="O49" s="16"/>
+      <c r="P49" s="16"/>
+      <c r="Q49" s="39"/>
+      <c r="R49" s="16"/>
+      <c r="S49" s="16"/>
+      <c r="T49" s="16"/>
+      <c r="U49" s="16"/>
+      <c r="V49" s="39"/>
+      <c r="W49" s="16"/>
+      <c r="X49" s="16"/>
+      <c r="Y49" s="16"/>
+      <c r="Z49" s="16"/>
+      <c r="AA49" s="39"/>
+    </row>
+    <row r="50" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B50" s="51" t="s">
+        <v>236</v>
+      </c>
+      <c r="C50" s="51"/>
+      <c r="D50" s="51"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="51"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="51"/>
+      <c r="I50" s="51"/>
+      <c r="J50" s="51">
+        <v>0.104</v>
+      </c>
+      <c r="K50" s="51"/>
+      <c r="L50" s="51"/>
+      <c r="M50" s="51"/>
+      <c r="N50" s="51"/>
+      <c r="O50" s="51">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="P50" s="51">
+        <v>0.106</v>
+      </c>
+      <c r="Q50" s="92"/>
+      <c r="R50" s="51">
+        <v>0.104</v>
+      </c>
+      <c r="S50" s="51">
+        <v>0.104</v>
+      </c>
+      <c r="T50" s="51">
+        <v>0.105</v>
+      </c>
+      <c r="U50" s="51">
+        <v>0.11</v>
+      </c>
+      <c r="V50" s="92"/>
+      <c r="W50" s="51">
+        <v>0.105</v>
+      </c>
+      <c r="X50" s="51">
+        <v>0.104</v>
+      </c>
+      <c r="Y50" s="51"/>
+      <c r="Z50" s="51"/>
+      <c r="AA50" s="92"/>
+    </row>
+    <row r="51" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B51" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="C51" s="51"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="51"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="51"/>
+      <c r="I51" s="51"/>
+      <c r="J51" s="51">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="K51" s="51"/>
+      <c r="L51" s="51"/>
+      <c r="M51" s="51"/>
+      <c r="N51" s="51"/>
+      <c r="O51" s="51">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="P51" s="51">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="Q51" s="92"/>
+      <c r="R51" s="51">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="S51" s="51">
+        <v>0.216</v>
+      </c>
+      <c r="T51" s="51">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="U51" s="51">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="V51" s="92"/>
+      <c r="W51" s="51">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="X51" s="51">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="Y51" s="51"/>
+      <c r="Z51" s="51"/>
+      <c r="AA51" s="92"/>
+    </row>
+    <row r="52" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B52" s="51" t="s">
+        <v>238</v>
+      </c>
+      <c r="C52" s="51"/>
+      <c r="D52" s="51"/>
+      <c r="E52" s="51"/>
+      <c r="F52" s="51"/>
+      <c r="G52" s="51"/>
+      <c r="H52" s="51"/>
+      <c r="I52" s="51"/>
+      <c r="J52" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="51"/>
+      <c r="M52" s="51"/>
+      <c r="N52" s="51"/>
+      <c r="O52" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="P52" s="51">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q52" s="92"/>
+      <c r="R52" s="51">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S52" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="T52" s="51">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U52" s="51">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="V52" s="92"/>
+      <c r="W52" s="51">
+        <v>3.1E-2</v>
+      </c>
+      <c r="X52" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="Y52" s="51"/>
+      <c r="Z52" s="51"/>
+      <c r="AA52" s="92"/>
+    </row>
+    <row r="53" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B53" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" s="51"/>
+      <c r="D53" s="51"/>
+      <c r="E53" s="51"/>
+      <c r="F53" s="51"/>
+      <c r="G53" s="51"/>
+      <c r="H53" s="51"/>
+      <c r="I53" s="51"/>
+      <c r="J53" s="51">
+        <v>0.187</v>
+      </c>
+      <c r="K53" s="51"/>
+      <c r="L53" s="51"/>
+      <c r="M53" s="51"/>
+      <c r="N53" s="51"/>
+      <c r="O53" s="51">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="P53" s="51">
+        <v>0.435</v>
+      </c>
+      <c r="Q53" s="92"/>
+      <c r="R53" s="51">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="S53" s="51">
+        <v>0.47599999999999998</v>
+      </c>
+      <c r="T53" s="51">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="U53" s="51">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="V53" s="92"/>
+      <c r="W53" s="51">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="X53" s="51">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="Y53" s="51"/>
+      <c r="Z53" s="51"/>
+      <c r="AA53" s="92"/>
+    </row>
+    <row r="54" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="Q54" s="37"/>
+      <c r="V54" s="37"/>
+      <c r="AA54" s="37"/>
+    </row>
+    <row r="55" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B55" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q55" s="37"/>
+      <c r="V55" s="37"/>
+      <c r="AA55" s="37"/>
+    </row>
+    <row r="56" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B56" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I56" s="15">
+        <v>321</v>
+      </c>
+      <c r="J56" s="15">
+        <v>358</v>
+      </c>
+      <c r="M56" s="15">
+        <v>381</v>
+      </c>
+      <c r="N56" s="15">
+        <v>391</v>
+      </c>
+      <c r="O56" s="15">
+        <v>379</v>
+      </c>
+      <c r="P56" s="15">
+        <v>365</v>
+      </c>
+      <c r="Q56" s="37">
+        <f>SUM(M56:P56)</f>
+        <v>1516</v>
+      </c>
+      <c r="R56" s="15">
+        <v>331</v>
+      </c>
+      <c r="S56" s="15">
+        <v>325</v>
+      </c>
+      <c r="T56" s="15">
+        <v>326</v>
+      </c>
+      <c r="U56" s="15">
+        <v>321</v>
+      </c>
+      <c r="V56" s="37">
+        <f>SUM(R56:U56)</f>
+        <v>1303</v>
+      </c>
+      <c r="W56" s="15">
+        <v>312</v>
+      </c>
+      <c r="X56" s="15">
+        <v>338</v>
+      </c>
+      <c r="AA56" s="37">
+        <f>SUM(W56:Z56)</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="57" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B57" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="I57" s="15">
+        <v>-163</v>
+      </c>
+      <c r="J57" s="15">
+        <v>-198</v>
+      </c>
+      <c r="M57" s="15">
+        <v>-222</v>
+      </c>
+      <c r="N57" s="15">
+        <v>-221</v>
+      </c>
+      <c r="O57" s="15">
+        <v>-210</v>
+      </c>
+      <c r="P57" s="15">
+        <v>-188</v>
+      </c>
+      <c r="Q57" s="37">
+        <f>SUM(M57:P57)</f>
+        <v>-841</v>
+      </c>
+      <c r="R57" s="15">
+        <v>-159</v>
+      </c>
+      <c r="S57" s="15">
+        <v>-148</v>
+      </c>
+      <c r="T57" s="15">
+        <v>-144</v>
+      </c>
+      <c r="U57" s="15">
+        <v>-143</v>
+      </c>
+      <c r="V57" s="37">
+        <f>SUM(R57:U57)</f>
+        <v>-594</v>
+      </c>
+      <c r="W57" s="15">
+        <v>-145</v>
+      </c>
+      <c r="X57" s="15">
+        <v>-161</v>
+      </c>
+      <c r="AA57" s="37">
+        <f>SUM(W57:Z57)</f>
+        <v>-306</v>
+      </c>
+    </row>
+    <row r="58" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B58" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" s="16">
+        <f t="shared" ref="C58" si="100">SUM(C56:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="16">
+        <f t="shared" ref="D58" si="101">SUM(D56:D57)</f>
+        <v>0</v>
+      </c>
+      <c r="E58" s="16">
+        <f t="shared" ref="E58" si="102">SUM(E56:E57)</f>
+        <v>0</v>
+      </c>
+      <c r="F58" s="16">
+        <f t="shared" ref="F58" si="103">SUM(F56:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="16">
+        <f t="shared" ref="G58" si="104">SUM(G56:G57)</f>
+        <v>0</v>
+      </c>
+      <c r="H58" s="16">
+        <f t="shared" ref="H58" si="105">SUM(H56:H57)</f>
+        <v>0</v>
+      </c>
+      <c r="I58" s="16">
+        <f t="shared" ref="I58" si="106">SUM(I56:I57)</f>
+        <v>158</v>
+      </c>
+      <c r="J58" s="16">
+        <f t="shared" ref="J58" si="107">SUM(J56:J57)</f>
+        <v>160</v>
+      </c>
+      <c r="K58" s="16">
+        <f t="shared" ref="K58" si="108">SUM(K56:K57)</f>
+        <v>0</v>
+      </c>
+      <c r="L58" s="16">
+        <f t="shared" ref="L58" si="109">SUM(L56:L57)</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="16">
+        <f t="shared" ref="M58" si="110">SUM(M56:M57)</f>
+        <v>159</v>
+      </c>
+      <c r="N58" s="16">
+        <f t="shared" ref="N58" si="111">SUM(N56:N57)</f>
+        <v>170</v>
+      </c>
+      <c r="O58" s="16">
+        <f t="shared" ref="O58" si="112">SUM(O56:O57)</f>
+        <v>169</v>
+      </c>
+      <c r="P58" s="16">
+        <f t="shared" ref="P58:Q58" si="113">SUM(P56:P57)</f>
+        <v>177</v>
+      </c>
+      <c r="Q58" s="39">
+        <f t="shared" si="113"/>
+        <v>675</v>
+      </c>
+      <c r="R58" s="16">
+        <f t="shared" ref="R58" si="114">SUM(R56:R57)</f>
+        <v>172</v>
+      </c>
+      <c r="S58" s="16">
+        <f t="shared" ref="S58" si="115">SUM(S56:S57)</f>
+        <v>177</v>
+      </c>
+      <c r="T58" s="16">
+        <f t="shared" ref="T58" si="116">SUM(T56:T57)</f>
+        <v>182</v>
+      </c>
+      <c r="U58" s="16">
+        <f t="shared" ref="U58:V58" si="117">SUM(U56:U57)</f>
+        <v>178</v>
+      </c>
+      <c r="V58" s="39">
+        <f t="shared" si="117"/>
+        <v>709</v>
+      </c>
+      <c r="W58" s="16">
+        <f t="shared" ref="W58" si="118">SUM(W56:W57)</f>
+        <v>167</v>
+      </c>
+      <c r="X58" s="16">
+        <f>SUM(X56:X57)</f>
+        <v>177</v>
+      </c>
+      <c r="Y58" s="16">
+        <f t="shared" ref="Y58:AA58" si="119">SUM(Y56:Y57)</f>
+        <v>0</v>
+      </c>
+      <c r="Z58" s="16">
+        <f t="shared" si="119"/>
+        <v>0</v>
+      </c>
+      <c r="AA58" s="39">
+        <f t="shared" si="119"/>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="59" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B59" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I59" s="15">
+        <v>1</v>
+      </c>
+      <c r="J59" s="15">
+        <v>1</v>
+      </c>
+      <c r="M59" s="15">
+        <v>1</v>
+      </c>
+      <c r="N59" s="15">
+        <v>1</v>
+      </c>
+      <c r="O59" s="15">
+        <v>1</v>
+      </c>
+      <c r="P59" s="15">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="37">
+        <f>SUM(M59:P59)</f>
+        <v>6</v>
+      </c>
+      <c r="R59" s="15">
+        <v>1</v>
+      </c>
+      <c r="S59" s="15">
+        <v>1</v>
+      </c>
+      <c r="T59" s="15">
+        <v>1</v>
+      </c>
+      <c r="U59" s="15">
+        <v>3</v>
+      </c>
+      <c r="V59" s="37">
+        <f>SUM(R59:U59)</f>
+        <v>6</v>
+      </c>
+      <c r="W59" s="15">
+        <v>1</v>
+      </c>
+      <c r="X59" s="15">
+        <v>1</v>
+      </c>
+      <c r="AA59" s="37">
+        <f>SUM(W59:Z59)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B60" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="I60" s="15">
+        <v>0</v>
+      </c>
+      <c r="J60" s="15">
+        <v>0</v>
+      </c>
+      <c r="M60" s="15">
+        <v>0</v>
+      </c>
+      <c r="N60" s="15">
+        <v>-1</v>
+      </c>
+      <c r="O60" s="15">
+        <v>0</v>
+      </c>
+      <c r="P60" s="15">
+        <v>-1</v>
+      </c>
+      <c r="Q60" s="37">
+        <f>SUM(M60:P60)</f>
+        <v>-2</v>
+      </c>
+      <c r="R60" s="15">
+        <v>0</v>
+      </c>
+      <c r="S60" s="15">
+        <v>0</v>
+      </c>
+      <c r="T60" s="15">
+        <v>0</v>
+      </c>
+      <c r="U60" s="15">
+        <v>0</v>
+      </c>
+      <c r="V60" s="37">
+        <f>SUM(R60:U60)</f>
+        <v>0</v>
+      </c>
+      <c r="W60" s="15">
+        <v>0</v>
+      </c>
+      <c r="X60" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="37">
+        <f>SUM(W60:Z60)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B61" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="I61" s="15">
+        <v>-1</v>
+      </c>
+      <c r="J61" s="15">
+        <v>1</v>
+      </c>
+      <c r="M61" s="15">
+        <v>-1</v>
+      </c>
+      <c r="N61" s="15">
+        <v>-2</v>
+      </c>
+      <c r="O61" s="15">
+        <v>-1</v>
+      </c>
+      <c r="P61" s="15">
+        <v>-1</v>
+      </c>
+      <c r="Q61" s="37">
+        <f>SUM(M61:P61)</f>
+        <v>-5</v>
+      </c>
+      <c r="R61" s="15">
+        <v>0</v>
+      </c>
+      <c r="S61" s="15">
+        <v>-3</v>
+      </c>
+      <c r="T61" s="15">
+        <v>-2</v>
+      </c>
+      <c r="U61" s="15">
+        <v>-2</v>
+      </c>
+      <c r="V61" s="37">
+        <f>SUM(R61:U61)</f>
+        <v>-7</v>
+      </c>
+      <c r="W61" s="15">
+        <v>0</v>
+      </c>
+      <c r="X61" s="15">
+        <v>-3</v>
+      </c>
+      <c r="AA61" s="37">
+        <f>SUM(W61:Z61)</f>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="62" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B62" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="16">
+        <f t="shared" ref="C62" si="120">SUM(C58:C61)</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="16">
+        <f t="shared" ref="D62" si="121">SUM(D58:D61)</f>
+        <v>0</v>
+      </c>
+      <c r="E62" s="16">
+        <f t="shared" ref="E62" si="122">SUM(E58:E61)</f>
+        <v>0</v>
+      </c>
+      <c r="F62" s="16">
+        <f t="shared" ref="F62" si="123">SUM(F58:F61)</f>
+        <v>0</v>
+      </c>
+      <c r="G62" s="16">
+        <f t="shared" ref="G62" si="124">SUM(G58:G61)</f>
+        <v>0</v>
+      </c>
+      <c r="H62" s="16">
+        <f t="shared" ref="H62" si="125">SUM(H58:H61)</f>
+        <v>0</v>
+      </c>
+      <c r="I62" s="16">
+        <f t="shared" ref="I62" si="126">SUM(I58:I61)</f>
+        <v>158</v>
+      </c>
+      <c r="J62" s="16">
+        <f t="shared" ref="J62" si="127">SUM(J58:J61)</f>
+        <v>162</v>
+      </c>
+      <c r="K62" s="16">
+        <f t="shared" ref="K62" si="128">SUM(K58:K61)</f>
+        <v>0</v>
+      </c>
+      <c r="L62" s="16">
+        <f t="shared" ref="L62" si="129">SUM(L58:L61)</f>
+        <v>0</v>
+      </c>
+      <c r="M62" s="16">
+        <f t="shared" ref="M62" si="130">SUM(M58:M61)</f>
+        <v>159</v>
+      </c>
+      <c r="N62" s="16">
+        <f t="shared" ref="N62" si="131">SUM(N58:N61)</f>
+        <v>168</v>
+      </c>
+      <c r="O62" s="16">
+        <f t="shared" ref="O62" si="132">SUM(O58:O61)</f>
+        <v>169</v>
+      </c>
+      <c r="P62" s="16">
+        <f t="shared" ref="P62:Q62" si="133">SUM(P58:P61)</f>
+        <v>178</v>
+      </c>
+      <c r="Q62" s="39">
+        <f t="shared" si="133"/>
+        <v>674</v>
+      </c>
+      <c r="R62" s="16">
+        <f t="shared" ref="R62" si="134">SUM(R58:R61)</f>
+        <v>173</v>
+      </c>
+      <c r="S62" s="16">
+        <f t="shared" ref="S62" si="135">SUM(S58:S61)</f>
+        <v>175</v>
+      </c>
+      <c r="T62" s="16">
+        <f t="shared" ref="T62" si="136">SUM(T58:T61)</f>
+        <v>181</v>
+      </c>
+      <c r="U62" s="16">
+        <f t="shared" ref="U62:V62" si="137">SUM(U58:U61)</f>
+        <v>179</v>
+      </c>
+      <c r="V62" s="39">
+        <f t="shared" si="137"/>
+        <v>708</v>
+      </c>
+      <c r="W62" s="16">
+        <f t="shared" ref="W62" si="138">SUM(W58:W61)</f>
+        <v>168</v>
+      </c>
+      <c r="X62" s="16">
+        <f>SUM(X58:X61)</f>
+        <v>175</v>
+      </c>
+      <c r="Y62" s="16">
+        <f t="shared" ref="Y62:AA62" si="139">SUM(Y58:Y61)</f>
+        <v>0</v>
+      </c>
+      <c r="Z62" s="16">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+      <c r="AA62" s="39">
+        <f t="shared" si="139"/>
+        <v>343</v>
+      </c>
+    </row>
+    <row r="63" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B63" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="I63" s="15">
+        <v>-39</v>
+      </c>
+      <c r="J63" s="15">
+        <v>-35</v>
+      </c>
+      <c r="M63" s="15">
+        <v>-37</v>
+      </c>
+      <c r="N63" s="15">
+        <v>-41</v>
+      </c>
+      <c r="O63" s="15">
+        <v>-33</v>
+      </c>
+      <c r="P63" s="15">
+        <v>-39</v>
+      </c>
+      <c r="Q63" s="37">
+        <f>SUM(M63:P63)</f>
+        <v>-150</v>
+      </c>
+      <c r="R63" s="15">
+        <v>-31</v>
+      </c>
+      <c r="S63" s="15">
+        <v>-34</v>
+      </c>
+      <c r="T63" s="15">
+        <v>-31</v>
+      </c>
+      <c r="U63" s="15">
+        <v>-37</v>
+      </c>
+      <c r="V63" s="37">
+        <f>SUM(R63:U63)</f>
+        <v>-133</v>
+      </c>
+      <c r="W63" s="15">
+        <v>-36</v>
+      </c>
+      <c r="X63" s="15">
+        <v>-39</v>
+      </c>
+      <c r="AA63" s="37">
+        <f>SUM(W63:Z63)</f>
+        <v>-75</v>
+      </c>
+    </row>
+    <row r="64" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B64" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I64" s="15">
+        <v>-1</v>
+      </c>
+      <c r="J64" s="15">
+        <v>0</v>
+      </c>
+      <c r="M64" s="15">
+        <v>-1</v>
+      </c>
+      <c r="N64" s="15">
+        <v>-1</v>
+      </c>
+      <c r="O64" s="15">
+        <v>-1</v>
+      </c>
+      <c r="P64" s="15">
+        <v>-1</v>
+      </c>
+      <c r="Q64" s="37">
+        <f>SUM(M64:P64)</f>
+        <v>-4</v>
+      </c>
+      <c r="R64" s="15">
+        <v>-1</v>
+      </c>
+      <c r="S64" s="15">
+        <v>-1</v>
+      </c>
+      <c r="T64" s="15">
+        <v>-1</v>
+      </c>
+      <c r="U64" s="15">
+        <v>-1</v>
+      </c>
+      <c r="V64" s="37">
+        <f>SUM(R64:U64)</f>
+        <v>-4</v>
+      </c>
+      <c r="W64" s="15">
+        <v>-1</v>
+      </c>
+      <c r="X64" s="15">
+        <v>-2</v>
+      </c>
+      <c r="AA64" s="37">
+        <f>SUM(W64:Z64)</f>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B65" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="I65" s="15">
+        <v>-19</v>
+      </c>
+      <c r="J65" s="15">
+        <v>-15</v>
+      </c>
+      <c r="M65" s="15">
+        <v>-8</v>
+      </c>
+      <c r="N65" s="15">
+        <v>-6</v>
+      </c>
+      <c r="O65" s="15">
+        <v>-4</v>
+      </c>
+      <c r="P65" s="15">
+        <v>-7</v>
+      </c>
+      <c r="Q65" s="37">
+        <f>SUM(M65:P65)</f>
+        <v>-25</v>
+      </c>
+      <c r="R65" s="15">
+        <v>-7</v>
+      </c>
+      <c r="S65" s="15">
+        <v>-6</v>
+      </c>
+      <c r="T65" s="15">
+        <v>-7</v>
+      </c>
+      <c r="U65" s="15">
+        <v>-8</v>
+      </c>
+      <c r="V65" s="37">
+        <f>SUM(R65:U65)</f>
+        <v>-28</v>
+      </c>
+      <c r="W65" s="15">
+        <v>-8</v>
+      </c>
+      <c r="X65" s="15">
+        <v>-9</v>
+      </c>
+      <c r="AA65" s="37">
+        <f>SUM(W65:Z65)</f>
+        <v>-17</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B66" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C66" s="16">
+        <f t="shared" ref="C66" si="140">SUM(C62:C65)</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="16">
+        <f t="shared" ref="D66" si="141">SUM(D62:D65)</f>
+        <v>0</v>
+      </c>
+      <c r="E66" s="16">
+        <f t="shared" ref="E66" si="142">SUM(E62:E65)</f>
+        <v>0</v>
+      </c>
+      <c r="F66" s="16">
+        <f t="shared" ref="F66" si="143">SUM(F62:F65)</f>
+        <v>0</v>
+      </c>
+      <c r="G66" s="16">
+        <f t="shared" ref="G66" si="144">SUM(G62:G65)</f>
+        <v>0</v>
+      </c>
+      <c r="H66" s="16">
+        <f t="shared" ref="H66" si="145">SUM(H62:H65)</f>
+        <v>0</v>
+      </c>
+      <c r="I66" s="16">
+        <f t="shared" ref="I66" si="146">SUM(I62:I65)</f>
+        <v>99</v>
+      </c>
+      <c r="J66" s="16">
+        <f t="shared" ref="J66" si="147">SUM(J62:J65)</f>
+        <v>112</v>
+      </c>
+      <c r="K66" s="16">
+        <f t="shared" ref="K66" si="148">SUM(K62:K65)</f>
+        <v>0</v>
+      </c>
+      <c r="L66" s="16">
+        <f t="shared" ref="L66" si="149">SUM(L62:L65)</f>
+        <v>0</v>
+      </c>
+      <c r="M66" s="16">
+        <f t="shared" ref="M66" si="150">SUM(M62:M65)</f>
+        <v>113</v>
+      </c>
+      <c r="N66" s="16">
+        <f t="shared" ref="N66" si="151">SUM(N62:N65)</f>
+        <v>120</v>
+      </c>
+      <c r="O66" s="16">
+        <f t="shared" ref="O66" si="152">SUM(O62:O65)</f>
+        <v>131</v>
+      </c>
+      <c r="P66" s="16">
+        <f t="shared" ref="P66:Q66" si="153">SUM(P62:P65)</f>
+        <v>131</v>
+      </c>
+      <c r="Q66" s="39">
+        <f t="shared" si="153"/>
+        <v>495</v>
+      </c>
+      <c r="R66" s="16">
+        <f t="shared" ref="R66" si="154">SUM(R62:R65)</f>
+        <v>134</v>
+      </c>
+      <c r="S66" s="16">
+        <f t="shared" ref="S66" si="155">SUM(S62:S65)</f>
+        <v>134</v>
+      </c>
+      <c r="T66" s="16">
+        <f t="shared" ref="T66" si="156">SUM(T62:T65)</f>
+        <v>142</v>
+      </c>
+      <c r="U66" s="16">
+        <f t="shared" ref="U66:V66" si="157">SUM(U62:U65)</f>
+        <v>133</v>
+      </c>
+      <c r="V66" s="39">
+        <f t="shared" si="157"/>
+        <v>543</v>
+      </c>
+      <c r="W66" s="16">
+        <f t="shared" ref="W66" si="158">SUM(W62:W65)</f>
+        <v>123</v>
+      </c>
+      <c r="X66" s="16">
+        <f>SUM(X62:X65)</f>
+        <v>125</v>
+      </c>
+      <c r="Y66" s="16">
+        <f t="shared" ref="Y66:AA66" si="159">SUM(Y62:Y65)</f>
+        <v>0</v>
+      </c>
+      <c r="Z66" s="16">
+        <f t="shared" si="159"/>
+        <v>0</v>
+      </c>
+      <c r="AA66" s="39">
+        <f t="shared" si="159"/>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B67" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I67" s="15">
+        <v>-5</v>
+      </c>
+      <c r="J67" s="15">
+        <v>-23</v>
+      </c>
+      <c r="M67" s="15">
+        <v>-2</v>
+      </c>
+      <c r="N67" s="15">
+        <v>-16</v>
+      </c>
+      <c r="O67" s="15">
+        <v>-8</v>
+      </c>
+      <c r="P67" s="15">
+        <v>3</v>
+      </c>
+      <c r="Q67" s="37">
+        <f>SUM(M67:P67)</f>
+        <v>-23</v>
+      </c>
+      <c r="R67" s="15">
+        <v>-8</v>
+      </c>
+      <c r="S67" s="15">
+        <v>-20</v>
+      </c>
+      <c r="T67" s="15">
+        <v>-16</v>
+      </c>
+      <c r="U67" s="15">
+        <v>-20</v>
+      </c>
+      <c r="V67" s="37">
+        <f>SUM(R67:U67)</f>
+        <v>-64</v>
+      </c>
+      <c r="W67" s="15">
+        <v>-2</v>
+      </c>
+      <c r="X67" s="15">
+        <v>-12</v>
+      </c>
+      <c r="AA67" s="37">
+        <f>SUM(W67:Z67)</f>
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B68" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="C68" s="16">
+        <f t="shared" ref="C68" si="160">SUM(C66:C67)</f>
+        <v>0</v>
+      </c>
+      <c r="D68" s="16">
+        <f t="shared" ref="D68" si="161">SUM(D66:D67)</f>
+        <v>0</v>
+      </c>
+      <c r="E68" s="16">
+        <f t="shared" ref="E68" si="162">SUM(E66:E67)</f>
+        <v>0</v>
+      </c>
+      <c r="F68" s="16">
+        <f t="shared" ref="F68" si="163">SUM(F66:F67)</f>
+        <v>0</v>
+      </c>
+      <c r="G68" s="16">
+        <f t="shared" ref="G68" si="164">SUM(G66:G67)</f>
+        <v>0</v>
+      </c>
+      <c r="H68" s="16">
+        <f t="shared" ref="H68" si="165">SUM(H66:H67)</f>
+        <v>0</v>
+      </c>
+      <c r="I68" s="16">
+        <f t="shared" ref="I68" si="166">SUM(I66:I67)</f>
+        <v>94</v>
+      </c>
+      <c r="J68" s="16">
+        <f t="shared" ref="J68" si="167">SUM(J66:J67)</f>
+        <v>89</v>
+      </c>
+      <c r="K68" s="16">
+        <f t="shared" ref="K68" si="168">SUM(K66:K67)</f>
+        <v>0</v>
+      </c>
+      <c r="L68" s="16">
+        <f t="shared" ref="L68" si="169">SUM(L66:L67)</f>
+        <v>0</v>
+      </c>
+      <c r="M68" s="16">
+        <f t="shared" ref="M68" si="170">SUM(M66:M67)</f>
+        <v>111</v>
+      </c>
+      <c r="N68" s="16">
+        <f t="shared" ref="N68" si="171">SUM(N66:N67)</f>
+        <v>104</v>
+      </c>
+      <c r="O68" s="16">
+        <f t="shared" ref="O68" si="172">SUM(O66:O67)</f>
+        <v>123</v>
+      </c>
+      <c r="P68" s="16">
+        <f t="shared" ref="P68:Q68" si="173">SUM(P66:P67)</f>
+        <v>134</v>
+      </c>
+      <c r="Q68" s="39">
+        <f t="shared" si="173"/>
+        <v>472</v>
+      </c>
+      <c r="R68" s="16">
+        <f t="shared" ref="R68" si="174">SUM(R66:R67)</f>
+        <v>126</v>
+      </c>
+      <c r="S68" s="16">
+        <f t="shared" ref="S68" si="175">SUM(S66:S67)</f>
+        <v>114</v>
+      </c>
+      <c r="T68" s="16">
+        <f t="shared" ref="T68" si="176">SUM(T66:T67)</f>
+        <v>126</v>
+      </c>
+      <c r="U68" s="16">
+        <f t="shared" ref="U68:V68" si="177">SUM(U66:U67)</f>
+        <v>113</v>
+      </c>
+      <c r="V68" s="39">
+        <f t="shared" si="177"/>
+        <v>479</v>
+      </c>
+      <c r="W68" s="16">
+        <f t="shared" ref="W68" si="178">SUM(W66:W67)</f>
+        <v>121</v>
+      </c>
+      <c r="X68" s="16">
+        <f>SUM(X66:X67)</f>
+        <v>113</v>
+      </c>
+      <c r="Y68" s="16">
+        <f t="shared" ref="Y68:AA68" si="179">SUM(Y66:Y67)</f>
+        <v>0</v>
+      </c>
+      <c r="Z68" s="16">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+      <c r="AA68" s="39">
+        <f t="shared" si="179"/>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B69" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q69" s="37"/>
+      <c r="R69" s="15">
+        <v>-27</v>
+      </c>
+      <c r="S69" s="15">
+        <v>-25</v>
+      </c>
+      <c r="T69" s="15">
+        <v>-28</v>
+      </c>
+      <c r="U69" s="15">
+        <v>-24</v>
+      </c>
+      <c r="V69" s="37">
+        <f>SUM(R69:U69)</f>
+        <v>-104</v>
+      </c>
+      <c r="W69" s="15">
+        <v>-30</v>
+      </c>
+      <c r="X69" s="15">
+        <v>-25</v>
+      </c>
+      <c r="AA69" s="37">
+        <f>SUM(W69:Z69)</f>
+        <v>-55</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B70" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q70" s="37"/>
+      <c r="R70" s="15">
+        <v>-4</v>
+      </c>
+      <c r="S70" s="15">
+        <v>-3</v>
+      </c>
+      <c r="T70" s="15">
+        <v>-3</v>
+      </c>
+      <c r="U70" s="15">
+        <v>-3</v>
+      </c>
+      <c r="V70" s="37">
+        <f>SUM(R70:U70)</f>
+        <v>-13</v>
+      </c>
+      <c r="W70" s="15">
+        <v>-3</v>
+      </c>
+      <c r="X70" s="15">
+        <v>-4</v>
+      </c>
+      <c r="AA70" s="37">
+        <f>SUM(W70:Z70)</f>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C71" s="89"/>
+      <c r="D71" s="89"/>
+      <c r="E71" s="89"/>
+      <c r="F71" s="89"/>
+      <c r="G71" s="89"/>
+      <c r="H71" s="89"/>
+      <c r="I71" s="89"/>
+      <c r="J71" s="89"/>
+      <c r="K71" s="89"/>
+      <c r="L71" s="89"/>
+      <c r="M71" s="89"/>
+      <c r="N71" s="89"/>
+      <c r="O71" s="89"/>
+      <c r="P71" s="16"/>
+      <c r="Q71" s="39"/>
+      <c r="R71" s="16">
+        <f t="shared" ref="R71" si="180">SUM(R68:R70)</f>
+        <v>95</v>
+      </c>
+      <c r="S71" s="16">
+        <f t="shared" ref="S71" si="181">SUM(S68:S70)</f>
+        <v>86</v>
+      </c>
+      <c r="T71" s="16">
+        <f t="shared" ref="T71" si="182">SUM(T68:T70)</f>
+        <v>95</v>
+      </c>
+      <c r="U71" s="16">
+        <f t="shared" ref="U71:V71" si="183">SUM(U68:U70)</f>
+        <v>86</v>
+      </c>
+      <c r="V71" s="39">
+        <f t="shared" si="183"/>
+        <v>362</v>
+      </c>
+      <c r="W71" s="16">
+        <f t="shared" ref="W71" si="184">SUM(W68:W70)</f>
+        <v>88</v>
+      </c>
+      <c r="X71" s="16">
+        <f>SUM(X68:X70)</f>
+        <v>84</v>
+      </c>
+      <c r="Y71" s="16">
+        <f t="shared" ref="Y71:AA71" si="185">SUM(Y68:Y70)</f>
+        <v>0</v>
+      </c>
+      <c r="Z71" s="16">
+        <f t="shared" si="185"/>
+        <v>0</v>
+      </c>
+      <c r="AA71" s="39">
+        <f t="shared" si="185"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B72" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C72" s="89"/>
+      <c r="D72" s="90"/>
+      <c r="E72" s="90"/>
+      <c r="F72" s="90"/>
+      <c r="G72" s="90"/>
+      <c r="H72" s="90"/>
+      <c r="I72" s="90"/>
+      <c r="J72" s="90"/>
+      <c r="K72" s="90"/>
+      <c r="L72" s="90"/>
+      <c r="M72" s="90"/>
+      <c r="N72" s="90"/>
+      <c r="O72" s="90"/>
+      <c r="Q72" s="37"/>
+      <c r="R72" s="15">
+        <v>500</v>
+      </c>
+      <c r="S72" s="15">
+        <v>500</v>
+      </c>
+      <c r="T72" s="15">
+        <v>500</v>
+      </c>
+      <c r="U72" s="15">
+        <v>500</v>
+      </c>
+      <c r="V72" s="37">
+        <v>500</v>
+      </c>
+      <c r="W72" s="15">
+        <v>500</v>
+      </c>
+      <c r="X72" s="15">
+        <v>500</v>
+      </c>
+      <c r="Y72" s="15">
+        <v>500</v>
+      </c>
+      <c r="Z72" s="15">
+        <v>500</v>
+      </c>
+      <c r="AA72" s="37">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="91"/>
+      <c r="D73" s="91"/>
+      <c r="E73" s="91"/>
+      <c r="F73" s="91"/>
+      <c r="G73" s="91"/>
+      <c r="H73" s="91"/>
+      <c r="I73" s="91"/>
+      <c r="J73" s="91"/>
+      <c r="K73" s="91"/>
+      <c r="L73" s="91"/>
+      <c r="M73" s="91"/>
+      <c r="N73" s="91"/>
+      <c r="O73" s="91"/>
+      <c r="P73" s="31"/>
+      <c r="Q73" s="93"/>
+      <c r="R73" s="31">
+        <f t="shared" ref="R73" si="186">R71/R72</f>
+        <v>0.19</v>
+      </c>
+      <c r="S73" s="31">
+        <f t="shared" ref="S73" si="187">S71/S72</f>
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="T73" s="31">
+        <f t="shared" ref="T73" si="188">T71/T72</f>
+        <v>0.19</v>
+      </c>
+      <c r="U73" s="31">
+        <f t="shared" ref="U73:V73" si="189">U71/U72</f>
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="V73" s="93">
+        <f t="shared" si="189"/>
+        <v>0.72399999999999998</v>
+      </c>
+      <c r="W73" s="31">
+        <f t="shared" ref="W73" si="190">W71/W72</f>
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="X73" s="31">
+        <f>X71/X72</f>
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="Y73" s="31">
+        <f t="shared" ref="Y73" si="191">Y71/Y72</f>
+        <v>0</v>
+      </c>
+      <c r="Z73" s="31">
+        <f t="shared" ref="Z73:AA73" si="192">Z71/Z72</f>
+        <v>0</v>
+      </c>
+      <c r="AA73" s="93">
+        <f t="shared" si="192"/>
+        <v>0.34399999999999997</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="16"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="16"/>
+      <c r="K74" s="16"/>
+      <c r="L74" s="16"/>
+      <c r="M74" s="16"/>
+      <c r="N74" s="16"/>
+      <c r="O74" s="16"/>
+      <c r="P74" s="16"/>
+      <c r="Q74" s="39"/>
+      <c r="R74" s="16"/>
+      <c r="S74" s="16"/>
+      <c r="T74" s="16"/>
+      <c r="U74" s="16"/>
+      <c r="V74" s="39"/>
+      <c r="W74" s="16"/>
+      <c r="X74" s="16"/>
+      <c r="Y74" s="16"/>
+      <c r="Z74" s="16"/>
+      <c r="AA74" s="39"/>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B75" s="51" t="s">
+        <v>236</v>
+      </c>
+      <c r="C75" s="51"/>
+      <c r="D75" s="51"/>
+      <c r="E75" s="51"/>
+      <c r="F75" s="51"/>
+      <c r="G75" s="51"/>
+      <c r="H75" s="51"/>
+      <c r="I75" s="51"/>
+      <c r="J75" s="51">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="K75" s="51"/>
+      <c r="L75" s="51"/>
+      <c r="M75" s="51"/>
+      <c r="N75" s="51"/>
+      <c r="O75" s="51">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="P75" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="Q75" s="92"/>
+      <c r="R75" s="51">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="S75" s="51">
+        <v>3.9E-2</v>
+      </c>
+      <c r="T75" s="51">
+        <v>3.9E-2</v>
+      </c>
+      <c r="U75" s="51">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="V75" s="92"/>
+      <c r="W75" s="51">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="X75" s="51">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y75" s="51"/>
+      <c r="Z75" s="51"/>
+      <c r="AA75" s="92"/>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B76" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="C76" s="51"/>
+      <c r="D76" s="51"/>
+      <c r="E76" s="51"/>
+      <c r="F76" s="51"/>
+      <c r="G76" s="51"/>
+      <c r="H76" s="51"/>
+      <c r="I76" s="51"/>
+      <c r="J76" s="51">
+        <v>0.312</v>
+      </c>
+      <c r="K76" s="51"/>
+      <c r="L76" s="51"/>
+      <c r="M76" s="51"/>
+      <c r="N76" s="51"/>
+      <c r="O76" s="51">
+        <v>0.222</v>
+      </c>
+      <c r="P76" s="51">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="Q76" s="92"/>
+      <c r="R76" s="51">
+        <v>0.222</v>
+      </c>
+      <c r="S76" s="51">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="T76" s="51">
+        <v>0.216</v>
+      </c>
+      <c r="U76" s="51">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="V76" s="92"/>
+      <c r="W76" s="51">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="X76" s="51">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="Y76" s="51"/>
+      <c r="Z76" s="51"/>
+      <c r="AA76" s="92"/>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B77" s="51" t="s">
+        <v>238</v>
+      </c>
+      <c r="C77" s="51"/>
+      <c r="D77" s="51"/>
+      <c r="E77" s="51"/>
+      <c r="F77" s="51"/>
+      <c r="G77" s="51"/>
+      <c r="H77" s="51"/>
+      <c r="I77" s="51"/>
+      <c r="J77" s="51">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="K77" s="51"/>
+      <c r="L77" s="51"/>
+      <c r="M77" s="51"/>
+      <c r="N77" s="51"/>
+      <c r="O77" s="51">
+        <v>2E-3</v>
+      </c>
+      <c r="P77" s="51">
+        <v>-1E-3</v>
+      </c>
+      <c r="Q77" s="92"/>
+      <c r="R77" s="51">
+        <v>2E-3</v>
+      </c>
+      <c r="S77" s="51">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="T77" s="51">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="U77" s="51">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="V77" s="92"/>
+      <c r="W77" s="51">
+        <v>0</v>
+      </c>
+      <c r="X77" s="51">
+        <v>2E-3</v>
+      </c>
+      <c r="Y77" s="51"/>
+      <c r="Z77" s="51"/>
+      <c r="AA77" s="92"/>
+    </row>
+    <row r="78" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B78" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C78" s="51"/>
+      <c r="D78" s="51"/>
+      <c r="E78" s="51"/>
+      <c r="F78" s="51"/>
+      <c r="G78" s="51"/>
+      <c r="H78" s="51"/>
+      <c r="I78" s="51"/>
+      <c r="J78" s="51">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="K78" s="51"/>
+      <c r="L78" s="51"/>
+      <c r="M78" s="51"/>
+      <c r="N78" s="51"/>
+      <c r="O78" s="51">
+        <v>0.38</v>
+      </c>
+      <c r="P78" s="51">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="Q78" s="92"/>
+      <c r="R78" s="51">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="S78" s="51">
+        <v>0.43</v>
+      </c>
+      <c r="T78" s="51">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="U78" s="51">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="V78" s="92"/>
+      <c r="W78" s="51">
+        <v>0.36599999999999999</v>
+      </c>
+      <c r="X78" s="51">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="Y78" s="51"/>
+      <c r="Z78" s="51"/>
+      <c r="AA78" s="92"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBE99104-313E-F047-A3AC-70F35D3A0BFC}">
   <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -11515,7 +15856,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="55" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -11525,618 +15866,661 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B4" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>194</v>
-      </c>
-      <c r="D4" s="64" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" s="63" t="s">
         <v>187</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="F4" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="F4" s="64" t="s">
+      <c r="G4" s="63" t="s">
         <v>189</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="H4" s="63" t="s">
         <v>190</v>
       </c>
-      <c r="H4" s="64" t="s">
-        <v>191</v>
-      </c>
-      <c r="I4" s="64" t="s">
+      <c r="I4" s="63" t="s">
+        <v>201</v>
+      </c>
+      <c r="J4" s="63" t="s">
         <v>202</v>
       </c>
-      <c r="J4" s="64" t="s">
+      <c r="K4" s="63" t="s">
         <v>203</v>
       </c>
-      <c r="K4" s="64" t="s">
+      <c r="L4" s="63" t="s">
         <v>204</v>
       </c>
-      <c r="L4" s="64" t="s">
+      <c r="M4" s="63" t="s">
         <v>205</v>
-      </c>
-      <c r="M4" s="64" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B5" s="57" t="s">
-        <v>185</v>
-      </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="66">
+        <v>184</v>
+      </c>
+      <c r="C5" s="64"/>
+      <c r="D5" s="65">
         <f>Modell!AD40</f>
         <v>0.123</v>
       </c>
-      <c r="E5" s="66">
+      <c r="E5" s="65">
         <f>Modell!AE40</f>
         <v>0.12000000000000008</v>
       </c>
-      <c r="F5" s="66">
+      <c r="F5" s="65">
         <f>Modell!AF40</f>
         <v>0.12000000000000018</v>
       </c>
-      <c r="G5" s="66">
+      <c r="G5" s="65">
         <f>Modell!AG40</f>
         <v>0.12000000000000008</v>
       </c>
-      <c r="H5" s="66">
+      <c r="H5" s="65">
         <f>Modell!AH40</f>
         <v>0.12000000000000012</v>
       </c>
-      <c r="I5" s="66">
+      <c r="I5" s="65">
         <f>Modell!AI40</f>
         <v>0.1000000000000001</v>
       </c>
-      <c r="J5" s="66">
+      <c r="J5" s="65">
         <f>Modell!AJ40</f>
         <v>0.10000000000000014</v>
       </c>
-      <c r="K5" s="66">
+      <c r="K5" s="65">
         <f>Modell!AK40</f>
         <v>0.10000000000000012</v>
       </c>
-      <c r="L5" s="66">
+      <c r="L5" s="65">
         <f>Modell!AL40</f>
         <v>0.10000000000000003</v>
       </c>
-      <c r="M5" s="66">
+      <c r="M5" s="65">
         <f>Modell!AM40</f>
         <v>0.1000000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="57" t="s">
-        <v>196</v>
-      </c>
-      <c r="C6" s="65"/>
-      <c r="D6" s="66">
+        <v>195</v>
+      </c>
+      <c r="C6" s="64"/>
+      <c r="D6" s="65">
         <v>0.13500000000000001</v>
       </c>
-      <c r="E6" s="66">
+      <c r="E6" s="65">
         <v>0.13500000000000001</v>
       </c>
-      <c r="F6" s="66">
+      <c r="F6" s="65">
         <v>0.13500000000000001</v>
       </c>
-      <c r="G6" s="66">
+      <c r="G6" s="65">
         <v>0.13500000000000001</v>
       </c>
-      <c r="H6" s="66">
+      <c r="H6" s="65">
         <v>0.13500000000000001</v>
       </c>
-      <c r="I6" s="66">
+      <c r="I6" s="65">
         <v>0.13500000000000001</v>
       </c>
-      <c r="J6" s="66">
+      <c r="J6" s="65">
         <v>0.13500000000000001</v>
       </c>
-      <c r="K6" s="66">
+      <c r="K6" s="65">
         <v>0.13500000000000001</v>
       </c>
-      <c r="L6" s="66">
+      <c r="L6" s="65">
         <v>0.13500000000000001</v>
       </c>
-      <c r="M6" s="66">
+      <c r="M6" s="65">
         <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B7" s="57" t="s">
-        <v>176</v>
-      </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="67">
+        <v>175</v>
+      </c>
+      <c r="C7" s="64"/>
+      <c r="D7" s="66">
         <f>Modell!AD20</f>
         <v>4176.7840000000015</v>
       </c>
-      <c r="E7" s="67">
+      <c r="E7" s="66">
         <f>Modell!AE20</f>
         <v>5071.0624000000043</v>
       </c>
-      <c r="F7" s="67">
+      <c r="F7" s="66">
         <f>Modell!AF20</f>
         <v>5755.3345600000048</v>
       </c>
-      <c r="G7" s="67">
+      <c r="G7" s="66">
         <f>Modell!AG20</f>
         <v>6416.7237216000076</v>
       </c>
-      <c r="H7" s="67">
+      <c r="H7" s="66">
         <f>Modell!AH20</f>
         <v>7184.7191235840091</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="67">
         <f>Modell!AI20</f>
         <v>8031.488911487364</v>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="67">
         <f>Modell!AJ20</f>
         <v>8929.3506620345324</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="67">
         <f>Modell!AK20</f>
         <v>9792.5655710746178</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="67">
         <f>Modell!AL20</f>
         <v>10740.898366303807</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="67">
         <f>Modell!AM20</f>
         <v>11782.824728199563</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B8" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="C8" s="65"/>
-      <c r="D8" s="66">
+        <v>192</v>
+      </c>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65">
         <v>0.78700000000000003</v>
       </c>
-      <c r="E8" s="66">
+      <c r="E8" s="65">
         <v>0.78700000000000003</v>
       </c>
-      <c r="F8" s="66">
+      <c r="F8" s="65">
         <v>0.78700000000000003</v>
       </c>
-      <c r="G8" s="66">
+      <c r="G8" s="65">
         <v>0.78700000000000003</v>
       </c>
-      <c r="H8" s="66">
+      <c r="H8" s="65">
         <v>0.78700000000000003</v>
       </c>
-      <c r="I8" s="66">
+      <c r="I8" s="65">
         <v>0.78700000000000003</v>
       </c>
-      <c r="J8" s="66">
+      <c r="J8" s="65">
         <v>0.78700000000000003</v>
       </c>
-      <c r="K8" s="66">
+      <c r="K8" s="65">
         <v>0.78700000000000003</v>
       </c>
-      <c r="L8" s="66">
+      <c r="L8" s="65">
         <v>0.78700000000000003</v>
       </c>
-      <c r="M8" s="66">
+      <c r="M8" s="65">
         <v>0.78700000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="65"/>
-      <c r="K9" s="65"/>
-      <c r="L9" s="65"/>
-      <c r="M9" s="65"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="64"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="64"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B10" s="58" t="s">
-        <v>177</v>
-      </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="65"/>
-      <c r="J10" s="65"/>
-      <c r="K10" s="65"/>
-      <c r="L10" s="65"/>
-      <c r="M10" s="65"/>
+        <v>176</v>
+      </c>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="64"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B11" s="60" t="s">
-        <v>186</v>
-      </c>
-      <c r="C11" s="67">
+      <c r="B11" s="59" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" s="66">
         <v>132341</v>
       </c>
-      <c r="D11" s="67">
+      <c r="D11" s="66">
         <f>C11*(1+D5)</f>
         <v>148618.943</v>
       </c>
-      <c r="E11" s="67">
+      <c r="E11" s="66">
         <f t="shared" ref="E11:H11" si="0">D11*(1+E5)</f>
         <v>166453.21616000001</v>
       </c>
-      <c r="F11" s="67">
+      <c r="F11" s="66">
         <f t="shared" si="0"/>
         <v>186427.60209920004</v>
       </c>
-      <c r="G11" s="67">
+      <c r="G11" s="66">
         <f t="shared" si="0"/>
         <v>208798.91435110406</v>
       </c>
-      <c r="H11" s="67">
+      <c r="H11" s="66">
         <f t="shared" si="0"/>
         <v>233854.78407323657</v>
       </c>
-      <c r="I11" s="67">
+      <c r="I11" s="66">
         <f t="shared" ref="I11:M11" si="1">H11*(1+I5)</f>
         <v>257240.26248056025</v>
       </c>
-      <c r="J11" s="67">
+      <c r="J11" s="66">
         <f t="shared" si="1"/>
         <v>282964.28872861632</v>
       </c>
-      <c r="K11" s="67">
+      <c r="K11" s="66">
         <f t="shared" si="1"/>
         <v>311260.71760147798</v>
       </c>
-      <c r="L11" s="67">
+      <c r="L11" s="66">
         <f t="shared" si="1"/>
         <v>342386.78936162579</v>
       </c>
-      <c r="M11" s="67">
+      <c r="M11" s="66">
         <f t="shared" si="1"/>
         <v>376625.46829778841</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B12" s="60" t="s">
-        <v>175</v>
-      </c>
-      <c r="C12" s="67">
+      <c r="B12" s="59" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="66">
         <v>104237</v>
       </c>
-      <c r="D12" s="67">
+      <c r="D12" s="66">
         <f>D11*D8</f>
         <v>116963.108141</v>
       </c>
-      <c r="E12" s="67">
+      <c r="E12" s="66">
         <f t="shared" ref="E12:H12" si="2">E11*E8</f>
         <v>130998.68111792002</v>
       </c>
-      <c r="F12" s="67">
+      <c r="F12" s="66">
         <f t="shared" si="2"/>
         <v>146718.52285207043</v>
       </c>
-      <c r="G12" s="67">
+      <c r="G12" s="66">
         <f t="shared" si="2"/>
         <v>164324.7455943189</v>
       </c>
-      <c r="H12" s="67">
+      <c r="H12" s="66">
         <f t="shared" si="2"/>
         <v>184043.7150656372</v>
       </c>
-      <c r="I12" s="67">
+      <c r="I12" s="66">
         <f t="shared" ref="I12" si="3">I11*I8</f>
         <v>202448.08657220093</v>
       </c>
-      <c r="J12" s="67">
+      <c r="J12" s="66">
         <f t="shared" ref="J12" si="4">J11*J8</f>
         <v>222692.89522942106</v>
       </c>
-      <c r="K12" s="67">
+      <c r="K12" s="66">
         <f t="shared" ref="K12" si="5">K11*K8</f>
         <v>244962.18475236319</v>
       </c>
-      <c r="L12" s="67">
+      <c r="L12" s="66">
         <f t="shared" ref="L12" si="6">L11*L8</f>
         <v>269458.40322759951</v>
       </c>
-      <c r="M12" s="67">
+      <c r="M12" s="66">
         <f>M11*M8</f>
         <v>296404.2435503595</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B13" s="60" t="s">
-        <v>178</v>
-      </c>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67">
+      <c r="B13" s="59" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66">
         <f>D12-C12</f>
         <v>12726.108141000004</v>
       </c>
-      <c r="E13" s="67">
+      <c r="E13" s="66">
         <f t="shared" ref="E13:H13" si="7">E12-D12</f>
         <v>14035.572976920012</v>
       </c>
-      <c r="F13" s="67">
+      <c r="F13" s="66">
         <f t="shared" si="7"/>
         <v>15719.84173415041</v>
       </c>
-      <c r="G13" s="67">
+      <c r="G13" s="66">
         <f t="shared" si="7"/>
         <v>17606.222742248472</v>
       </c>
-      <c r="H13" s="67">
+      <c r="H13" s="66">
         <f t="shared" si="7"/>
         <v>19718.969471318298</v>
       </c>
-      <c r="I13" s="67">
+      <c r="I13" s="66">
         <f t="shared" ref="I13" si="8">I12-H12</f>
         <v>18404.371506563737</v>
       </c>
-      <c r="J13" s="67">
+      <c r="J13" s="66">
         <f t="shared" ref="J13" si="9">J12-I12</f>
         <v>20244.808657220128</v>
       </c>
-      <c r="K13" s="67">
+      <c r="K13" s="66">
         <f t="shared" ref="K13" si="10">K12-J12</f>
         <v>22269.289522942126</v>
       </c>
-      <c r="L13" s="67">
+      <c r="L13" s="66">
         <f t="shared" ref="L13" si="11">L12-K12</f>
         <v>24496.218475236325</v>
       </c>
-      <c r="M13" s="67">
+      <c r="M13" s="66">
         <f>M12-L12</f>
         <v>26945.840322759992</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B14" s="60" t="s">
-        <v>197</v>
-      </c>
-      <c r="C14" s="67">
+      <c r="B14" s="59" t="s">
+        <v>196</v>
+      </c>
+      <c r="C14" s="66">
         <v>14246</v>
       </c>
-      <c r="D14" s="67">
+      <c r="D14" s="66">
         <f>D12*D6</f>
         <v>15790.019599035002</v>
       </c>
-      <c r="E14" s="67">
+      <c r="E14" s="66">
         <f t="shared" ref="E14:H14" si="12">E12*E6</f>
         <v>17684.821950919202</v>
       </c>
-      <c r="F14" s="67">
+      <c r="F14" s="66">
         <f t="shared" si="12"/>
         <v>19807.000585029509</v>
       </c>
-      <c r="G14" s="67">
+      <c r="G14" s="66">
         <f t="shared" si="12"/>
         <v>22183.840655233053</v>
       </c>
-      <c r="H14" s="67">
+      <c r="H14" s="66">
         <f t="shared" si="12"/>
         <v>24845.901533861022</v>
       </c>
-      <c r="I14" s="67">
-        <f t="shared" ref="I14:M14" si="13">I12*I6</f>
+      <c r="I14" s="66">
+        <f t="shared" ref="I14:L14" si="13">I12*I6</f>
         <v>27330.491687247129</v>
       </c>
-      <c r="J14" s="67">
+      <c r="J14" s="66">
         <f t="shared" si="13"/>
         <v>30063.540855971845</v>
       </c>
-      <c r="K14" s="67">
+      <c r="K14" s="66">
         <f t="shared" si="13"/>
         <v>33069.894941569029</v>
       </c>
-      <c r="L14" s="67">
+      <c r="L14" s="66">
         <f t="shared" si="13"/>
         <v>36376.884435725937</v>
       </c>
-      <c r="M14" s="67">
+      <c r="M14" s="66">
         <f>M12*M6</f>
         <v>40014.572879298539</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B15" s="61" t="s">
-        <v>199</v>
-      </c>
-      <c r="C15" s="69">
+      <c r="B15" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="C15" s="68">
         <f>C14/C12</f>
         <v>0.1366693208745455</v>
       </c>
-      <c r="D15" s="69">
+      <c r="D15" s="68">
         <f>D14/D12</f>
         <v>0.13500000000000001</v>
       </c>
-      <c r="E15" s="69">
+      <c r="E15" s="68">
         <f t="shared" ref="E15:H15" si="14">E14/E12</f>
         <v>0.13500000000000001</v>
       </c>
-      <c r="F15" s="69">
+      <c r="F15" s="68">
         <f t="shared" si="14"/>
         <v>0.13500000000000001</v>
       </c>
-      <c r="G15" s="69">
+      <c r="G15" s="68">
         <f t="shared" si="14"/>
         <v>0.13500000000000001</v>
       </c>
-      <c r="H15" s="69">
+      <c r="H15" s="68">
         <f t="shared" si="14"/>
         <v>0.13500000000000001</v>
       </c>
-      <c r="I15" s="69">
+      <c r="I15" s="68">
         <f t="shared" ref="I15" si="15">I14/I12</f>
         <v>0.13500000000000001</v>
       </c>
-      <c r="J15" s="69">
+      <c r="J15" s="68">
         <f t="shared" ref="J15" si="16">J14/J12</f>
         <v>0.13500000000000001</v>
       </c>
-      <c r="K15" s="69">
+      <c r="K15" s="68">
         <f t="shared" ref="K15" si="17">K14/K12</f>
         <v>0.13500000000000001</v>
       </c>
-      <c r="L15" s="69">
+      <c r="L15" s="68">
         <f t="shared" ref="L15" si="18">L14/L12</f>
         <v>0.13500000000000001</v>
       </c>
-      <c r="M15" s="69">
+      <c r="M15" s="68">
         <f t="shared" ref="M15" si="19">M14/M12</f>
         <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B16" s="60" t="s">
-        <v>200</v>
-      </c>
-      <c r="C16" s="67"/>
-      <c r="D16" s="67">
+      <c r="B16" s="59" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66">
         <f>D14-C14</f>
         <v>1544.0195990350021</v>
       </c>
-      <c r="E16" s="67">
+      <c r="E16" s="66">
         <f t="shared" ref="E16:H16" si="20">E14-D14</f>
         <v>1894.8023518842001</v>
       </c>
-      <c r="F16" s="67">
+      <c r="F16" s="66">
         <f t="shared" si="20"/>
         <v>2122.178634110307</v>
       </c>
-      <c r="G16" s="67">
+      <c r="G16" s="66">
         <f t="shared" si="20"/>
         <v>2376.8400702035433</v>
       </c>
-      <c r="H16" s="67">
+      <c r="H16" s="66">
         <f t="shared" si="20"/>
         <v>2662.0608786279699</v>
       </c>
-      <c r="I16" s="67">
-        <f t="shared" ref="I16:M16" si="21">I14-H14</f>
+      <c r="I16" s="66">
+        <f t="shared" ref="I16:L16" si="21">I14-H14</f>
         <v>2484.590153386107</v>
       </c>
-      <c r="J16" s="67">
+      <c r="J16" s="66">
         <f t="shared" si="21"/>
         <v>2733.0491687247159</v>
       </c>
-      <c r="K16" s="67">
+      <c r="K16" s="66">
         <f t="shared" si="21"/>
         <v>3006.3540855971842</v>
       </c>
-      <c r="L16" s="67">
+      <c r="L16" s="66">
         <f t="shared" si="21"/>
         <v>3306.9894941569073</v>
       </c>
-      <c r="M16" s="67">
+      <c r="M16" s="66">
         <f>M14-L14</f>
         <v>3637.6884435726024</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B17" s="62" t="s">
-        <v>201</v>
-      </c>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70">
+      <c r="B17" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69">
         <f>D7-D16</f>
         <v>2632.7644009649994</v>
       </c>
-      <c r="E17" s="70">
+      <c r="E17" s="69">
         <f t="shared" ref="E17:H17" si="22">E7-E16</f>
         <v>3176.2600481158042</v>
       </c>
-      <c r="F17" s="70">
+      <c r="F17" s="69">
         <f t="shared" si="22"/>
         <v>3633.1559258896978</v>
       </c>
-      <c r="G17" s="70">
+      <c r="G17" s="69">
         <f t="shared" si="22"/>
         <v>4039.8836513964643</v>
       </c>
-      <c r="H17" s="70">
+      <c r="H17" s="69">
         <f t="shared" si="22"/>
         <v>4522.6582449560392</v>
       </c>
-      <c r="I17" s="70">
+      <c r="I17" s="69">
         <f t="shared" ref="I17" si="23">I7-I16</f>
         <v>5546.898758101257</v>
       </c>
-      <c r="J17" s="70">
+      <c r="J17" s="69">
         <f t="shared" ref="J17" si="24">J7-J16</f>
         <v>6196.3014933098166</v>
       </c>
-      <c r="K17" s="70">
+      <c r="K17" s="69">
         <f t="shared" ref="K17" si="25">K7-K16</f>
         <v>6786.2114854774336</v>
       </c>
-      <c r="L17" s="70">
+      <c r="L17" s="69">
         <f t="shared" ref="L17" si="26">L7-L16</f>
         <v>7433.9088721468997</v>
       </c>
-      <c r="M17" s="70">
+      <c r="M17" s="69">
         <f>M7-M16</f>
         <v>8145.1362846269603</v>
       </c>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B18" s="63" t="s">
-        <v>207</v>
-      </c>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71">
+      <c r="B18" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70">
         <f>D17/D7</f>
         <v>0.63033290707994438</v>
       </c>
-      <c r="E18" s="71">
+      <c r="E18" s="70">
         <f t="shared" ref="E18:H18" si="27">E17/E7</f>
         <v>0.6263500224560048</v>
       </c>
-      <c r="F18" s="71">
+      <c r="F18" s="70">
         <f t="shared" si="27"/>
         <v>0.63126754631092974</v>
       </c>
-      <c r="G18" s="71">
+      <c r="G18" s="70">
         <f t="shared" si="27"/>
         <v>0.62958665927868884</v>
       </c>
-      <c r="H18" s="71">
+      <c r="H18" s="70">
         <f t="shared" si="27"/>
         <v>0.62948295781115604</v>
       </c>
-      <c r="I18" s="71">
+      <c r="I18" s="70">
         <f t="shared" ref="I18" si="28">I17/I7</f>
         <v>0.6906438917157165</v>
       </c>
-      <c r="J18" s="71">
+      <c r="J18" s="70">
         <f t="shared" ref="J18" si="29">J17/J7</f>
         <v>0.69392520551970382</v>
       </c>
-      <c r="K18" s="71">
+      <c r="K18" s="70">
         <f t="shared" ref="K18" si="30">K17/K7</f>
         <v>0.69299627724961232</v>
       </c>
-      <c r="L18" s="71">
+      <c r="L18" s="70">
         <f t="shared" ref="L18" si="31">L17/L7</f>
         <v>0.69211239308142536</v>
       </c>
-      <c r="M18" s="71">
+      <c r="M18" s="70">
         <f t="shared" ref="M18" si="32">M17/M7</f>
         <v>0.69127195494416493</v>
       </c>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="D20" s="59"/>
+    <row r="20" spans="2:13" s="95" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="94" t="s">
+        <v>239</v>
+      </c>
+      <c r="C20" s="96"/>
+      <c r="D20" s="97">
+        <f>D17/Modell!$B$6</f>
+        <v>6.1227079092209286E-2</v>
+      </c>
+      <c r="E20" s="97">
+        <f>E17/Modell!$B$6</f>
+        <v>7.3866512746879165E-2</v>
+      </c>
+      <c r="F20" s="97">
+        <f>F17/Modell!$B$6</f>
+        <v>8.4491998276504596E-2</v>
+      </c>
+      <c r="G20" s="97">
+        <f>G17/Modell!$B$6</f>
+        <v>9.3950782590615442E-2</v>
+      </c>
+      <c r="H20" s="97">
+        <f>H17/Modell!$B$6</f>
+        <v>0.10517809871990789</v>
+      </c>
+      <c r="I20" s="97">
+        <f>I17/Modell!$B$6</f>
+        <v>0.12899764553723853</v>
+      </c>
+      <c r="J20" s="97">
+        <f>J17/Modell!$B$6</f>
+        <v>0.14410003472813526</v>
+      </c>
+      <c r="K20" s="97">
+        <f>K17/Modell!$B$6</f>
+        <v>0.15781887175528916</v>
+      </c>
+      <c r="L20" s="97">
+        <f>L17/Modell!$B$6</f>
+        <v>0.17288160167783487</v>
+      </c>
+      <c r="M20" s="97">
+        <f>M17/Modell!$B$6</f>
+        <v>0.18942177406109209</v>
+      </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.2">
       <c r="G25" s="56" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.2">
@@ -12149,7 +16533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD94E57-B20A-A94B-9310-31E181295B22}">
   <dimension ref="A1:W62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -12161,12 +16545,12 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -12222,26 +16606,26 @@
         <v>30</v>
       </c>
       <c r="S4" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="T4" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="U4" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="V4" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J6" s="15">
         <v>41662</v>
@@ -12279,7 +16663,7 @@
     </row>
     <row r="7" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J7" s="15">
         <v>2068</v>
@@ -12317,7 +16701,7 @@
     </row>
     <row r="8" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J8" s="15">
         <v>4334</v>
@@ -12355,12 +16739,12 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J10" s="15">
         <v>25283</v>
@@ -12398,7 +16782,7 @@
     </row>
     <row r="11" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J11" s="15">
         <v>2213</v>
@@ -12436,7 +16820,7 @@
     </row>
     <row r="12" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J12" s="15">
         <v>4805</v>
@@ -12474,12 +16858,12 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J14" s="15">
         <v>21864</v>
@@ -12517,7 +16901,7 @@
     </row>
     <row r="15" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J15" s="15">
         <v>1552</v>
@@ -12555,7 +16939,7 @@
     </row>
     <row r="16" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J16" s="15">
         <v>3289</v>
@@ -12593,12 +16977,12 @@
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="2:20" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J18" s="15">
         <v>6634</v>
@@ -12636,7 +17020,7 @@
     </row>
     <row r="19" spans="2:20" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J19" s="15">
         <v>312</v>
@@ -12674,7 +17058,7 @@
     </row>
     <row r="20" spans="2:20" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J20" s="15">
         <v>722</v>
@@ -12712,12 +17096,12 @@
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="2:20" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J22" s="15">
         <v>2551</v>
@@ -12755,7 +17139,7 @@
     </row>
     <row r="23" spans="2:20" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J23" s="15">
         <v>101</v>
@@ -12793,7 +17177,7 @@
     </row>
     <row r="24" spans="2:20" s="45" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J24" s="45">
         <v>542</v>
@@ -12831,7 +17215,7 @@
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C26" s="15">
         <f t="shared" ref="C26:S26" si="0">C6+C10+C14+C18+C22</f>
@@ -12908,7 +17292,7 @@
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C27" s="15">
         <f t="shared" ref="C27:S28" si="1">C7+C11+C15+C19+C23</f>
@@ -12985,7 +17369,7 @@
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C28" s="15">
         <f t="shared" si="1"/>
@@ -13062,7 +17446,7 @@
     </row>
     <row r="29" spans="2:20" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C29" s="48">
         <f t="shared" ref="C29:S29" si="3">SUM(C26:C28)</f>
@@ -13139,7 +17523,7 @@
     </row>
     <row r="30" spans="2:20" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C30" s="24" t="e">
         <f t="shared" ref="C30:S30" si="4">C26/C29</f>
@@ -13216,7 +17600,7 @@
     </row>
     <row r="31" spans="2:20" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C31" s="24" t="e">
         <f t="shared" ref="C31:S31" si="5">C27/C29</f>
@@ -13293,7 +17677,7 @@
     </row>
     <row r="32" spans="2:20" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C32" s="24" t="e">
         <f t="shared" ref="C32:S32" si="6">C28/C29</f>
@@ -13370,7 +17754,7 @@
     </row>
     <row r="33" spans="1:22" s="49" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="49" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" s="49" t="e">
         <f t="shared" ref="C33:S33" si="7">SUM(C30:C32)</f>
@@ -13475,12 +17859,12 @@
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="15"/>
@@ -13527,7 +17911,7 @@
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C40" s="15"/>
       <c r="D40" s="15"/>
@@ -13574,7 +17958,7 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="15"/>
@@ -13621,12 +18005,12 @@
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
@@ -13673,7 +18057,7 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
@@ -13720,7 +18104,7 @@
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C45" s="15"/>
       <c r="D45" s="15"/>
@@ -13767,12 +18151,12 @@
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C47" s="15"/>
       <c r="D47" s="15"/>
@@ -13819,7 +18203,7 @@
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C48" s="15"/>
       <c r="D48" s="15"/>
@@ -13866,7 +18250,7 @@
     </row>
     <row r="49" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15"/>
@@ -13913,12 +18297,12 @@
     </row>
     <row r="50" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C51" s="15"/>
       <c r="D51" s="15"/>
@@ -13948,7 +18332,7 @@
     </row>
     <row r="52" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C52" s="15"/>
       <c r="D52" s="15"/>
@@ -13977,7 +18361,7 @@
     </row>
     <row r="53" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15"/>
@@ -14006,7 +18390,7 @@
     </row>
     <row r="55" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C55" s="15">
         <f>C39+C43+C47+C51</f>
@@ -14091,7 +18475,7 @@
     </row>
     <row r="56" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C56" s="15">
         <f>C40+C44+C48+C52</f>
@@ -14176,7 +18560,7 @@
     </row>
     <row r="57" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B57" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C57" s="15">
         <f>C41+C45+C49+C53</f>
@@ -14261,7 +18645,7 @@
     </row>
     <row r="58" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B58" s="47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C58" s="48">
         <f>SUM(C55:C57)</f>
@@ -14346,7 +18730,7 @@
     </row>
     <row r="59" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B59" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C59" s="24" t="e">
         <f>C55/C58</f>
@@ -14431,7 +18815,7 @@
     </row>
     <row r="60" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B60" s="24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C60" s="24" t="e">
         <f>C56/C58</f>
@@ -14516,7 +18900,7 @@
     </row>
     <row r="61" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B61" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C61" s="24" t="e">
         <f>C57/C58</f>
@@ -14601,7 +18985,7 @@
     </row>
     <row r="62" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B62" s="49" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C62" s="49" t="e">
         <f>SUM(C59:C61)</f>
@@ -14690,7 +19074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1BC336F-0535-604A-AD69-88DBD7978E92}">
   <dimension ref="A1:V82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -14702,12 +19086,12 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -14763,26 +19147,26 @@
         <v>30</v>
       </c>
       <c r="S4" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="T4" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="U4" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="V4" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J6" s="15">
         <v>-789</v>
@@ -14820,7 +19204,7 @@
     </row>
     <row r="7" spans="1:22" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C7" s="19" t="e">
         <f>-C6/'Kvalitet bok (Gross)'!C6</f>
@@ -14897,7 +19281,7 @@
     </row>
     <row r="8" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J8" s="15">
         <v>-364</v>
@@ -14935,7 +19319,7 @@
     </row>
     <row r="9" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C9" s="19" t="e">
         <f>-C8/'Kvalitet bok (Gross)'!C7</f>
@@ -15012,7 +19396,7 @@
     </row>
     <row r="10" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J10" s="15">
         <v>-2088</v>
@@ -15050,7 +19434,7 @@
     </row>
     <row r="11" spans="1:22" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C11" s="19" t="e">
         <f>-C10/'Kvalitet bok (Gross)'!C8</f>
@@ -15127,12 +19511,12 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J13" s="15">
         <v>-524</v>
@@ -15170,7 +19554,7 @@
     </row>
     <row r="14" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C14" s="19" t="e">
         <f>-C13/'Kvalitet bok (Gross)'!C10</f>
@@ -15247,7 +19631,7 @@
     </row>
     <row r="15" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J15" s="15">
         <v>-419</v>
@@ -15285,7 +19669,7 @@
     </row>
     <row r="16" spans="1:22" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="19" t="e">
         <f>-C15/'Kvalitet bok (Gross)'!C11</f>
@@ -15362,7 +19746,7 @@
     </row>
     <row r="17" spans="2:20" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J17" s="15">
         <v>-1952</v>
@@ -15400,7 +19784,7 @@
     </row>
     <row r="18" spans="2:20" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C18" s="19" t="e">
         <f>-C17/'Kvalitet bok (Gross)'!C12</f>
@@ -15477,12 +19861,12 @@
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="2:20" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J20" s="15">
         <v>-198</v>
@@ -15520,7 +19904,7 @@
     </row>
     <row r="21" spans="2:20" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C21" s="19" t="e">
         <f>-C20/'Kvalitet bok (Gross)'!C14</f>
@@ -15597,7 +19981,7 @@
     </row>
     <row r="22" spans="2:20" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J22" s="15">
         <v>-141</v>
@@ -15635,7 +20019,7 @@
     </row>
     <row r="23" spans="2:20" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C23" s="19" t="e">
         <f>-C22/'Kvalitet bok (Gross)'!C15</f>
@@ -15712,7 +20096,7 @@
     </row>
     <row r="24" spans="2:20" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J24" s="15">
         <v>-1182</v>
@@ -15750,7 +20134,7 @@
     </row>
     <row r="25" spans="2:20" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C25" s="19" t="e">
         <f>-C24/'Kvalitet bok (Gross)'!C16</f>
@@ -15827,12 +20211,12 @@
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="2:20" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J27" s="15">
         <v>-118</v>
@@ -15870,7 +20254,7 @@
     </row>
     <row r="28" spans="2:20" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C28" s="19" t="e">
         <f>-C27/'Kvalitet bok (Gross)'!C18</f>
@@ -15947,7 +20331,7 @@
     </row>
     <row r="29" spans="2:20" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J29" s="15">
         <v>-47</v>
@@ -15985,7 +20369,7 @@
     </row>
     <row r="30" spans="2:20" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C30" s="19" t="e">
         <f>-C29/'Kvalitet bok (Gross)'!C19</f>
@@ -16062,7 +20446,7 @@
     </row>
     <row r="31" spans="2:20" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J31" s="15">
         <v>-362</v>
@@ -16100,7 +20484,7 @@
     </row>
     <row r="32" spans="2:20" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C32" s="19" t="e">
         <f>-C31/'Kvalitet bok (Gross)'!C20</f>
@@ -16177,12 +20561,12 @@
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J34" s="15">
         <v>-84</v>
@@ -16220,7 +20604,7 @@
     </row>
     <row r="35" spans="1:22" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C35" s="19" t="e">
         <f>-C34/'Kvalitet bok (Gross)'!C22</f>
@@ -16297,7 +20681,7 @@
     </row>
     <row r="36" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J36" s="15">
         <v>-24</v>
@@ -16335,7 +20719,7 @@
     </row>
     <row r="37" spans="1:22" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C37" s="19" t="e">
         <f>-C36/'Kvalitet bok (Gross)'!C23</f>
@@ -16412,7 +20796,7 @@
     </row>
     <row r="38" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J38" s="15">
         <v>-397</v>
@@ -16450,7 +20834,7 @@
     </row>
     <row r="39" spans="1:22" s="50" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C39" s="50" t="e">
         <f>-C38/'Kvalitet bok (Gross)'!C24</f>
@@ -16527,7 +20911,7 @@
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="15">
         <f t="shared" ref="C40:T40" si="0">C6+C13+C20+C27+C34</f>
@@ -16604,7 +20988,7 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C41" s="15">
         <f t="shared" ref="C41:T41" si="1">C8+C15+C22+C29+C36</f>
@@ -16681,7 +21065,7 @@
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C42" s="15">
         <f t="shared" ref="C42:S42" si="2">C10+C17+C24+C31+C38</f>
@@ -16758,7 +21142,7 @@
     </row>
     <row r="43" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C43" s="16">
         <f t="shared" ref="C43:S43" si="3">SUM(C40:C42)</f>
@@ -16833,80 +21217,80 @@
         <v>-13495</v>
       </c>
     </row>
-    <row r="44" spans="1:22" s="79" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22" s="78" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="21"/>
-      <c r="B44" s="79" t="s">
-        <v>157</v>
-      </c>
-      <c r="C44" s="79" t="e">
+      <c r="B44" s="78" t="s">
+        <v>156</v>
+      </c>
+      <c r="C44" s="78" t="e">
         <f>-C43/'Kvalitet bok (Gross)'!C29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D44" s="79" t="e">
+      <c r="D44" s="78" t="e">
         <f>-D43/'Kvalitet bok (Gross)'!D29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E44" s="79" t="e">
+      <c r="E44" s="78" t="e">
         <f>-E43/'Kvalitet bok (Gross)'!E29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F44" s="79" t="e">
+      <c r="F44" s="78" t="e">
         <f>-F43/'Kvalitet bok (Gross)'!F29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G44" s="79" t="e">
+      <c r="G44" s="78" t="e">
         <f>-G43/'Kvalitet bok (Gross)'!G29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H44" s="79" t="e">
+      <c r="H44" s="78" t="e">
         <f>-H43/'Kvalitet bok (Gross)'!H29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I44" s="79" t="e">
+      <c r="I44" s="78" t="e">
         <f>-I43/'Kvalitet bok (Gross)'!I29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J44" s="79">
+      <c r="J44" s="78">
         <f>-J43/'Kvalitet bok (Gross)'!J29</f>
         <v>7.3678051758640575E-2</v>
       </c>
-      <c r="K44" s="79">
+      <c r="K44" s="78">
         <f>-K43/'Kvalitet bok (Gross)'!K29</f>
         <v>7.8729730608000523E-2</v>
       </c>
-      <c r="L44" s="79">
+      <c r="L44" s="78">
         <f>-L43/'Kvalitet bok (Gross)'!L29</f>
         <v>8.1089013874455607E-2</v>
       </c>
-      <c r="M44" s="79">
+      <c r="M44" s="78">
         <f>-M43/'Kvalitet bok (Gross)'!M29</f>
         <v>8.3302086760891028E-2</v>
       </c>
-      <c r="N44" s="79">
+      <c r="N44" s="78">
         <f>-N43/'Kvalitet bok (Gross)'!N29</f>
         <v>8.6552978186983584E-2</v>
       </c>
-      <c r="O44" s="79">
+      <c r="O44" s="78">
         <f>-O43/'Kvalitet bok (Gross)'!O29</f>
         <v>8.4958259018899598E-2</v>
       </c>
-      <c r="P44" s="79">
+      <c r="P44" s="78">
         <f>-P43/'Kvalitet bok (Gross)'!P29</f>
         <v>8.5889347334104679E-2</v>
       </c>
-      <c r="Q44" s="79">
+      <c r="Q44" s="78">
         <f>-Q43/'Kvalitet bok (Gross)'!Q29</f>
         <v>8.7247374957660606E-2</v>
       </c>
-      <c r="R44" s="79">
+      <c r="R44" s="78">
         <f>-R43/'Kvalitet bok (Gross)'!R29</f>
         <v>8.6049763549359504E-2</v>
       </c>
-      <c r="S44" s="79">
+      <c r="S44" s="78">
         <f>-S43/'Kvalitet bok (Gross)'!S29</f>
         <v>8.6150206503869439E-2</v>
       </c>
-      <c r="T44" s="79">
+      <c r="T44" s="78">
         <f>-T43/'Kvalitet bok (Gross)'!T29</f>
         <v>8.7490680411034388E-2</v>
       </c>
@@ -16943,12 +21327,12 @@
     </row>
     <row r="49" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C50" s="15"/>
       <c r="D50" s="15"/>
@@ -16995,7 +21379,7 @@
     </row>
     <row r="51" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B51" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C51" s="19"/>
       <c r="D51" s="19"/>
@@ -17053,7 +21437,7 @@
     </row>
     <row r="52" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C52" s="15"/>
       <c r="D52" s="15"/>
@@ -17100,7 +21484,7 @@
     </row>
     <row r="53" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B53" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C53" s="19"/>
       <c r="D53" s="19"/>
@@ -17158,7 +21542,7 @@
     </row>
     <row r="54" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C54" s="15"/>
       <c r="D54" s="15"/>
@@ -17205,7 +21589,7 @@
     </row>
     <row r="55" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B55" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C55" s="19"/>
       <c r="D55" s="19"/>
@@ -17263,12 +21647,12 @@
     </row>
     <row r="56" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C57" s="15"/>
       <c r="D57" s="15"/>
@@ -17315,7 +21699,7 @@
     </row>
     <row r="58" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B58" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C58" s="19"/>
       <c r="D58" s="19"/>
@@ -17373,7 +21757,7 @@
     </row>
     <row r="59" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="15"/>
@@ -17420,7 +21804,7 @@
     </row>
     <row r="60" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B60" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
@@ -17478,7 +21862,7 @@
     </row>
     <row r="61" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C61" s="15"/>
       <c r="D61" s="15"/>
@@ -17525,7 +21909,7 @@
     </row>
     <row r="62" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B62" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C62" s="19"/>
       <c r="D62" s="19"/>
@@ -17583,12 +21967,12 @@
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C64" s="15"/>
       <c r="D64" s="15"/>
@@ -17635,7 +22019,7 @@
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B65" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C65" s="19"/>
       <c r="D65" s="19"/>
@@ -17693,7 +22077,7 @@
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C66" s="15"/>
       <c r="D66" s="15"/>
@@ -17740,7 +22124,7 @@
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B67" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C67" s="19"/>
       <c r="D67" s="19"/>
@@ -17798,7 +22182,7 @@
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C68" s="15"/>
       <c r="D68" s="15"/>
@@ -17845,7 +22229,7 @@
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B69" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C69" s="19"/>
       <c r="D69" s="19"/>
@@ -17903,12 +22287,12 @@
     </row>
     <row r="70" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="15"/>
@@ -17937,7 +22321,7 @@
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B72" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C72" s="19"/>
       <c r="D72" s="19"/>
@@ -17968,7 +22352,7 @@
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="15"/>
@@ -17997,7 +22381,7 @@
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B74" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C74" s="19"/>
       <c r="D74" s="19"/>
@@ -18028,7 +22412,7 @@
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C75" s="15"/>
       <c r="D75" s="15"/>
@@ -18057,7 +22441,7 @@
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B76" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C76" s="19"/>
       <c r="D76" s="19"/>
@@ -18088,7 +22472,7 @@
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B78" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C78" s="15">
         <f>C50+C57+C64+C71</f>
@@ -18173,7 +22557,7 @@
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B79" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C79" s="15">
         <f>C52+C59+C66+C73</f>
@@ -18258,7 +22642,7 @@
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B80" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C80" s="15">
         <f>C54+C61+C68+C75</f>
@@ -18343,7 +22727,7 @@
     </row>
     <row r="81" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C81" s="16">
         <f>SUM(C78:C80)</f>
@@ -18414,7 +22798,7 @@
         <v>-12891</v>
       </c>
       <c r="T81" s="16">
-        <f t="shared" si="7"/>
+        <f>SUM(T78:T80)</f>
         <v>-13495</v>
       </c>
       <c r="U81" s="1">
@@ -18427,86 +22811,86 @@
       </c>
     </row>
     <row r="82" spans="2:22" s="1" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="79" t="s">
-        <v>157</v>
-      </c>
-      <c r="C82" s="79" t="e">
+      <c r="B82" s="78" t="s">
+        <v>156</v>
+      </c>
+      <c r="C82" s="78" t="e">
         <f>-C81/'Kvalitet bok (Gross)'!C58</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D82" s="79" t="e">
+      <c r="D82" s="78" t="e">
         <f>-D81/'Kvalitet bok (Gross)'!D58</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E82" s="79" t="e">
+      <c r="E82" s="78" t="e">
         <f>-E81/'Kvalitet bok (Gross)'!E58</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F82" s="79" t="e">
+      <c r="F82" s="78" t="e">
         <f>-F81/'Kvalitet bok (Gross)'!F58</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G82" s="79" t="e">
+      <c r="G82" s="78" t="e">
         <f>-G81/'Kvalitet bok (Gross)'!G58</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H82" s="79" t="e">
+      <c r="H82" s="78" t="e">
         <f>-H81/'Kvalitet bok (Gross)'!H58</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I82" s="79" t="e">
+      <c r="I82" s="78" t="e">
         <f>-I81/'Kvalitet bok (Gross)'!I58</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J82" s="79">
+      <c r="J82" s="78">
         <f>-J81/'Kvalitet bok (Gross)'!J58</f>
         <v>7.3678051758640575E-2</v>
       </c>
-      <c r="K82" s="79">
+      <c r="K82" s="78">
         <f>-K81/'Kvalitet bok (Gross)'!K58</f>
         <v>7.8729730608000523E-2</v>
       </c>
-      <c r="L82" s="79">
+      <c r="L82" s="78">
         <f>-L81/'Kvalitet bok (Gross)'!L58</f>
         <v>8.1089013874455607E-2</v>
       </c>
-      <c r="M82" s="79">
+      <c r="M82" s="78">
         <f>-M81/'Kvalitet bok (Gross)'!M58</f>
         <v>8.3302086760891028E-2</v>
       </c>
-      <c r="N82" s="79">
+      <c r="N82" s="78">
         <f>-N81/'Kvalitet bok (Gross)'!N58</f>
         <v>8.6544253809598182E-2</v>
       </c>
-      <c r="O82" s="79">
+      <c r="O82" s="78">
         <f>-O81/'Kvalitet bok (Gross)'!O58</f>
         <v>8.4943907794455972E-2</v>
       </c>
-      <c r="P82" s="79">
+      <c r="P82" s="78">
         <f>-P81/'Kvalitet bok (Gross)'!P58</f>
         <v>8.5890597370087099E-2</v>
       </c>
-      <c r="Q82" s="79">
+      <c r="Q82" s="78">
         <f>-Q81/'Kvalitet bok (Gross)'!Q58</f>
         <v>8.7246759295195223E-2</v>
       </c>
-      <c r="R82" s="79">
+      <c r="R82" s="78">
         <f>-R81/'Kvalitet bok (Gross)'!R58</f>
         <v>8.6049158902145956E-2</v>
       </c>
-      <c r="S82" s="79">
+      <c r="S82" s="78">
         <f>-S81/'Kvalitet bok (Gross)'!S58</f>
         <v>8.614905504023096E-2</v>
       </c>
-      <c r="T82" s="79">
+      <c r="T82" s="78">
         <f>-T81/'Kvalitet bok (Gross)'!T58</f>
         <v>8.7489545987928449E-2</v>
       </c>
-      <c r="U82" s="79" t="e">
+      <c r="U82" s="78" t="e">
         <f>-U81/'Kvalitet bok (Gross)'!U58</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V82" s="79" t="e">
+      <c r="V82" s="78" t="e">
         <f>-V81/'Kvalitet bok (Gross)'!V58</f>
         <v>#DIV/0!</v>
       </c>
@@ -18517,7 +22901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA24FBF3-2E91-1F49-970E-14FE8E3410CF}">
   <dimension ref="B3:V19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -18580,16 +22964,16 @@
         <v>30</v>
       </c>
       <c r="S3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="T3" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="U3" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="V3" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.25">
@@ -18616,7 +23000,7 @@
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G5" s="2">
         <v>-178</v>
@@ -18663,7 +23047,7 @@
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G6" s="2">
         <v>-30</v>
@@ -18710,7 +23094,7 @@
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G7" s="2">
         <v>-561</v>
@@ -18757,7 +23141,7 @@
     </row>
     <row r="8" spans="2:22" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C8" s="16">
         <f t="shared" ref="C8:S8" si="0">SUM(C5:C7)</f>
@@ -18834,7 +23218,7 @@
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G10" s="2">
         <v>-9</v>
@@ -18881,7 +23265,7 @@
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
@@ -18928,7 +23312,7 @@
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
@@ -18975,7 +23359,7 @@
     </row>
     <row r="13" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" ref="C13:S13" si="1">SUM(C10:C12)</f>
@@ -19052,7 +23436,7 @@
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G15" s="2">
         <v>-45</v>
@@ -19099,7 +23483,7 @@
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
@@ -19146,7 +23530,7 @@
     </row>
     <row r="17" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" ref="C17:S17" si="2">SUM(C15:C16)</f>
@@ -19223,7 +23607,7 @@
     </row>
     <row r="19" spans="2:20" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C19" s="16">
         <f t="shared" ref="C19:S19" si="3">C8+C13+C17</f>
@@ -19303,72 +23687,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF2445BF-A756-E84D-AD46-CF66A6613A3B}">
   <dimension ref="A2:A25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="52" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEC8E745-DC06-8448-81B5-DC40131426CF}">
-  <dimension ref="C4:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="3:6" ht="62" x14ac:dyDescent="0.7">
-      <c r="C4" s="7"/>
-      <c r="D4" s="7">
-        <v>2026</v>
-      </c>
-      <c r="E4" s="7">
-        <v>2027</v>
-      </c>
-      <c r="F4" s="7">
-        <v>2028</v>
-      </c>
-    </row>
-    <row r="5" spans="3:6" ht="62" x14ac:dyDescent="0.7">
-      <c r="C5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="33">
-        <f>Modell!$B$4/Modell!AD22</f>
-        <v>10.414711414332171</v>
-      </c>
-      <c r="E5" s="33">
-        <f>Modell!$B$4/Modell!AE22</f>
-        <v>8.5780841505716765</v>
-      </c>
-      <c r="F5" s="33">
-        <f>Modell!$B$4/Modell!AF22</f>
-        <v>7.558205269651598</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>